--- a/InputData/elec/CRbQ/Cap Retirements before Quantization.xlsx
+++ b/InputData/elec/CRbQ/Cap Retirements before Quantization.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Postdoc Projects/eps-indonesia-cpl/InputData/elec/CRbQ/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AF32893-9FC0-444A-805C-3136FF01F963}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE139A42-4913-6D4C-891D-6F30696E1BAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21360" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -218,7 +218,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -238,7 +238,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="11" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3595,7 +3594,7 @@
         <v>0</v>
       </c>
       <c r="H2" s="10">
-        <v>1100</v>
+        <v>4200</v>
       </c>
       <c r="I2" s="10">
         <v>0</v>
@@ -3610,7 +3609,7 @@
         <v>0</v>
       </c>
       <c r="M2" s="10">
-        <v>1000</v>
+        <v>1900</v>
       </c>
       <c r="N2" s="10">
         <v>0</v>
@@ -3640,7 +3639,7 @@
         <v>0</v>
       </c>
       <c r="W2" s="10">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X2" s="10">
         <v>0</v>
@@ -3655,82 +3654,82 @@
         <v>0</v>
       </c>
       <c r="AB2" s="10">
-        <v>24000</v>
+        <v>0</v>
       </c>
       <c r="AC2" s="10">
-        <v>22100.000000000364</v>
+        <v>0</v>
       </c>
       <c r="AD2" s="10">
-        <v>20200.000000000273</v>
+        <v>0</v>
       </c>
       <c r="AE2" s="10">
-        <v>18300.000000000182</v>
+        <v>0</v>
       </c>
       <c r="AF2" s="10">
-        <v>16400.000000000091</v>
+        <v>0</v>
       </c>
       <c r="AG2" s="10">
-        <v>14500</v>
-      </c>
-      <c r="AH2" s="11">
-        <v>12600.000000000364</v>
+        <v>0</v>
+      </c>
+      <c r="AH2" s="10">
+        <v>0</v>
       </c>
       <c r="AI2" s="10">
-        <v>10700.000000000273</v>
-      </c>
-      <c r="AJ2" s="11">
-        <v>8800.0000000001819</v>
-      </c>
-      <c r="AK2" s="11">
-        <v>6900.0000000000909</v>
-      </c>
-      <c r="AL2" s="11">
-        <v>5000</v>
-      </c>
-      <c r="AM2" s="11">
-        <v>3623.1884057970537</v>
-      </c>
-      <c r="AN2" s="11">
-        <v>2625.498844780439</v>
-      </c>
-      <c r="AO2" s="11">
-        <v>1902.5353947684089</v>
-      </c>
-      <c r="AP2" s="11">
-        <v>1378.6488367886841</v>
-      </c>
-      <c r="AQ2" s="11">
-        <v>999.02089622367089</v>
-      </c>
-      <c r="AR2" s="11">
-        <v>723.92818566931714</v>
-      </c>
-      <c r="AS2" s="11">
-        <v>524.5856417893533</v>
-      </c>
-      <c r="AT2" s="11">
-        <v>380.13452303575821</v>
-      </c>
-      <c r="AU2" s="11">
-        <v>275.45979930127044</v>
-      </c>
-      <c r="AV2" s="11">
-        <v>199.60855021830932</v>
-      </c>
-      <c r="AW2" s="11">
-        <v>144.64387696978744</v>
-      </c>
-      <c r="AX2" s="11">
-        <v>104.81440360129388</v>
-      </c>
-      <c r="AY2" s="11">
-        <v>75.952466377748195</v>
-      </c>
-      <c r="AZ2" s="11">
-        <v>55.038019114309556</v>
-      </c>
-      <c r="BA2" s="11">
-        <v>39.882622546600608</v>
+        <v>0</v>
+      </c>
+      <c r="AJ2" s="10">
+        <v>0</v>
+      </c>
+      <c r="AK2" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL2" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM2" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN2" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO2" s="10">
+        <v>0</v>
+      </c>
+      <c r="AP2" s="10">
+        <v>0</v>
+      </c>
+      <c r="AQ2" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR2" s="10">
+        <v>0</v>
+      </c>
+      <c r="AS2" s="10">
+        <v>0</v>
+      </c>
+      <c r="AT2" s="10">
+        <v>0</v>
+      </c>
+      <c r="AU2" s="10">
+        <v>0</v>
+      </c>
+      <c r="AV2" s="10">
+        <v>0</v>
+      </c>
+      <c r="AW2" s="10">
+        <v>0</v>
+      </c>
+      <c r="AX2" s="10">
+        <v>0</v>
+      </c>
+      <c r="AY2" s="10">
+        <v>0</v>
+      </c>
+      <c r="AZ2" s="10">
+        <v>0</v>
+      </c>
+      <c r="BA2" s="10">
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3833,64 +3832,64 @@
       <c r="AG3" s="10">
         <v>0</v>
       </c>
-      <c r="AH3" s="11">
+      <c r="AH3" s="10">
         <v>0</v>
       </c>
       <c r="AI3" s="10">
         <v>0</v>
       </c>
-      <c r="AJ3" s="11">
-        <v>0</v>
-      </c>
-      <c r="AK3" s="11">
-        <v>0</v>
-      </c>
-      <c r="AL3" s="11">
-        <v>0</v>
-      </c>
-      <c r="AM3" s="11">
-        <v>0</v>
-      </c>
-      <c r="AN3" s="11">
-        <v>0</v>
-      </c>
-      <c r="AO3" s="11">
-        <v>0</v>
-      </c>
-      <c r="AP3" s="11">
-        <v>0</v>
-      </c>
-      <c r="AQ3" s="11">
-        <v>0</v>
-      </c>
-      <c r="AR3" s="11">
-        <v>0</v>
-      </c>
-      <c r="AS3" s="11">
-        <v>0</v>
-      </c>
-      <c r="AT3" s="11">
-        <v>0</v>
-      </c>
-      <c r="AU3" s="11">
-        <v>0</v>
-      </c>
-      <c r="AV3" s="11">
-        <v>0</v>
-      </c>
-      <c r="AW3" s="11">
-        <v>0</v>
-      </c>
-      <c r="AX3" s="11">
-        <v>0</v>
-      </c>
-      <c r="AY3" s="11">
-        <v>0</v>
-      </c>
-      <c r="AZ3" s="11">
-        <v>0</v>
-      </c>
-      <c r="BA3" s="11">
+      <c r="AJ3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AK3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AP3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AQ3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AS3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AT3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AU3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AV3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AW3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AX3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AY3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AZ3" s="10">
+        <v>0</v>
+      </c>
+      <c r="BA3" s="10">
         <v>0</v>
       </c>
     </row>
@@ -3994,64 +3993,64 @@
       <c r="AG4" s="10">
         <v>0</v>
       </c>
-      <c r="AH4" s="11">
+      <c r="AH4" s="10">
         <v>0</v>
       </c>
       <c r="AI4" s="10">
         <v>0</v>
       </c>
-      <c r="AJ4" s="11">
-        <v>0</v>
-      </c>
-      <c r="AK4" s="11">
-        <v>0</v>
-      </c>
-      <c r="AL4" s="11">
-        <v>0</v>
-      </c>
-      <c r="AM4" s="11">
-        <v>0</v>
-      </c>
-      <c r="AN4" s="11">
-        <v>0</v>
-      </c>
-      <c r="AO4" s="11">
-        <v>0</v>
-      </c>
-      <c r="AP4" s="11">
-        <v>0</v>
-      </c>
-      <c r="AQ4" s="11">
-        <v>0</v>
-      </c>
-      <c r="AR4" s="11">
-        <v>0</v>
-      </c>
-      <c r="AS4" s="11">
-        <v>0</v>
-      </c>
-      <c r="AT4" s="11">
-        <v>0</v>
-      </c>
-      <c r="AU4" s="11">
-        <v>0</v>
-      </c>
-      <c r="AV4" s="11">
-        <v>0</v>
-      </c>
-      <c r="AW4" s="11">
-        <v>0</v>
-      </c>
-      <c r="AX4" s="11">
-        <v>0</v>
-      </c>
-      <c r="AY4" s="11">
-        <v>0</v>
-      </c>
-      <c r="AZ4" s="11">
-        <v>0</v>
-      </c>
-      <c r="BA4" s="11">
+      <c r="AJ4" s="10">
+        <v>0</v>
+      </c>
+      <c r="AK4" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL4" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM4" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN4" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO4" s="10">
+        <v>0</v>
+      </c>
+      <c r="AP4" s="10">
+        <v>0</v>
+      </c>
+      <c r="AQ4" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR4" s="10">
+        <v>0</v>
+      </c>
+      <c r="AS4" s="10">
+        <v>0</v>
+      </c>
+      <c r="AT4" s="10">
+        <v>0</v>
+      </c>
+      <c r="AU4" s="10">
+        <v>0</v>
+      </c>
+      <c r="AV4" s="10">
+        <v>0</v>
+      </c>
+      <c r="AW4" s="10">
+        <v>0</v>
+      </c>
+      <c r="AX4" s="10">
+        <v>0</v>
+      </c>
+      <c r="AY4" s="10">
+        <v>0</v>
+      </c>
+      <c r="AZ4" s="10">
+        <v>0</v>
+      </c>
+      <c r="BA4" s="10">
         <v>0</v>
       </c>
     </row>
@@ -4155,64 +4154,64 @@
       <c r="AG5" s="10">
         <v>0</v>
       </c>
-      <c r="AH5" s="11">
+      <c r="AH5" s="10">
         <v>0</v>
       </c>
       <c r="AI5" s="10">
         <v>0</v>
       </c>
-      <c r="AJ5" s="11">
-        <v>0</v>
-      </c>
-      <c r="AK5" s="11">
-        <v>0</v>
-      </c>
-      <c r="AL5" s="11">
-        <v>0</v>
-      </c>
-      <c r="AM5" s="11">
-        <v>0</v>
-      </c>
-      <c r="AN5" s="11">
-        <v>0</v>
-      </c>
-      <c r="AO5" s="11">
-        <v>0</v>
-      </c>
-      <c r="AP5" s="11">
-        <v>0</v>
-      </c>
-      <c r="AQ5" s="11">
-        <v>0</v>
-      </c>
-      <c r="AR5" s="11">
-        <v>0</v>
-      </c>
-      <c r="AS5" s="11">
-        <v>0</v>
-      </c>
-      <c r="AT5" s="11">
-        <v>0</v>
-      </c>
-      <c r="AU5" s="11">
-        <v>0</v>
-      </c>
-      <c r="AV5" s="11">
-        <v>0</v>
-      </c>
-      <c r="AW5" s="11">
-        <v>0</v>
-      </c>
-      <c r="AX5" s="11">
-        <v>0</v>
-      </c>
-      <c r="AY5" s="11">
-        <v>0</v>
-      </c>
-      <c r="AZ5" s="11">
-        <v>0</v>
-      </c>
-      <c r="BA5" s="11">
+      <c r="AJ5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AK5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AP5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AQ5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AS5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AT5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AU5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AV5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AW5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AX5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AY5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AZ5" s="10">
+        <v>0</v>
+      </c>
+      <c r="BA5" s="10">
         <v>0</v>
       </c>
     </row>
@@ -4316,64 +4315,64 @@
       <c r="AG6" s="10">
         <v>0</v>
       </c>
-      <c r="AH6" s="11">
+      <c r="AH6" s="10">
         <v>0</v>
       </c>
       <c r="AI6" s="10">
         <v>0</v>
       </c>
-      <c r="AJ6" s="11">
-        <v>0</v>
-      </c>
-      <c r="AK6" s="11">
-        <v>0</v>
-      </c>
-      <c r="AL6" s="11">
-        <v>0</v>
-      </c>
-      <c r="AM6" s="11">
-        <v>0</v>
-      </c>
-      <c r="AN6" s="11">
-        <v>0</v>
-      </c>
-      <c r="AO6" s="11">
-        <v>0</v>
-      </c>
-      <c r="AP6" s="11">
-        <v>0</v>
-      </c>
-      <c r="AQ6" s="11">
-        <v>0</v>
-      </c>
-      <c r="AR6" s="11">
-        <v>0</v>
-      </c>
-      <c r="AS6" s="11">
-        <v>0</v>
-      </c>
-      <c r="AT6" s="11">
-        <v>0</v>
-      </c>
-      <c r="AU6" s="11">
-        <v>0</v>
-      </c>
-      <c r="AV6" s="11">
-        <v>0</v>
-      </c>
-      <c r="AW6" s="11">
-        <v>0</v>
-      </c>
-      <c r="AX6" s="11">
-        <v>0</v>
-      </c>
-      <c r="AY6" s="11">
-        <v>0</v>
-      </c>
-      <c r="AZ6" s="11">
-        <v>0</v>
-      </c>
-      <c r="BA6" s="11">
+      <c r="AJ6" s="10">
+        <v>0</v>
+      </c>
+      <c r="AK6" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL6" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM6" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN6" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO6" s="10">
+        <v>0</v>
+      </c>
+      <c r="AP6" s="10">
+        <v>0</v>
+      </c>
+      <c r="AQ6" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR6" s="10">
+        <v>0</v>
+      </c>
+      <c r="AS6" s="10">
+        <v>0</v>
+      </c>
+      <c r="AT6" s="10">
+        <v>0</v>
+      </c>
+      <c r="AU6" s="10">
+        <v>0</v>
+      </c>
+      <c r="AV6" s="10">
+        <v>0</v>
+      </c>
+      <c r="AW6" s="10">
+        <v>0</v>
+      </c>
+      <c r="AX6" s="10">
+        <v>0</v>
+      </c>
+      <c r="AY6" s="10">
+        <v>0</v>
+      </c>
+      <c r="AZ6" s="10">
+        <v>0</v>
+      </c>
+      <c r="BA6" s="10">
         <v>0</v>
       </c>
     </row>
@@ -4477,64 +4476,64 @@
       <c r="AG7" s="10">
         <v>0</v>
       </c>
-      <c r="AH7" s="11">
+      <c r="AH7" s="10">
         <v>0</v>
       </c>
       <c r="AI7" s="10">
         <v>0</v>
       </c>
-      <c r="AJ7" s="11">
-        <v>0</v>
-      </c>
-      <c r="AK7" s="11">
-        <v>0</v>
-      </c>
-      <c r="AL7" s="11">
-        <v>0</v>
-      </c>
-      <c r="AM7" s="11">
-        <v>0</v>
-      </c>
-      <c r="AN7" s="11">
-        <v>0</v>
-      </c>
-      <c r="AO7" s="11">
-        <v>0</v>
-      </c>
-      <c r="AP7" s="11">
-        <v>0</v>
-      </c>
-      <c r="AQ7" s="11">
-        <v>0</v>
-      </c>
-      <c r="AR7" s="11">
-        <v>0</v>
-      </c>
-      <c r="AS7" s="11">
-        <v>0</v>
-      </c>
-      <c r="AT7" s="11">
-        <v>0</v>
-      </c>
-      <c r="AU7" s="11">
-        <v>0</v>
-      </c>
-      <c r="AV7" s="11">
-        <v>0</v>
-      </c>
-      <c r="AW7" s="11">
-        <v>0</v>
-      </c>
-      <c r="AX7" s="11">
-        <v>0</v>
-      </c>
-      <c r="AY7" s="11">
-        <v>0</v>
-      </c>
-      <c r="AZ7" s="11">
-        <v>0</v>
-      </c>
-      <c r="BA7" s="11">
+      <c r="AJ7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AK7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AP7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AQ7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AS7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AT7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AU7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AV7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AW7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AX7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AY7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AZ7" s="10">
+        <v>0</v>
+      </c>
+      <c r="BA7" s="10">
         <v>0</v>
       </c>
     </row>
@@ -4638,64 +4637,64 @@
       <c r="AG8" s="10">
         <v>0</v>
       </c>
-      <c r="AH8" s="11">
+      <c r="AH8" s="10">
         <v>0</v>
       </c>
       <c r="AI8" s="10">
         <v>0</v>
       </c>
-      <c r="AJ8" s="11">
-        <v>0</v>
-      </c>
-      <c r="AK8" s="11">
-        <v>0</v>
-      </c>
-      <c r="AL8" s="11">
-        <v>0</v>
-      </c>
-      <c r="AM8" s="11">
-        <v>0</v>
-      </c>
-      <c r="AN8" s="11">
-        <v>0</v>
-      </c>
-      <c r="AO8" s="11">
-        <v>0</v>
-      </c>
-      <c r="AP8" s="11">
-        <v>0</v>
-      </c>
-      <c r="AQ8" s="11">
-        <v>0</v>
-      </c>
-      <c r="AR8" s="11">
-        <v>0</v>
-      </c>
-      <c r="AS8" s="11">
-        <v>0</v>
-      </c>
-      <c r="AT8" s="11">
-        <v>0</v>
-      </c>
-      <c r="AU8" s="11">
-        <v>0</v>
-      </c>
-      <c r="AV8" s="11">
-        <v>0</v>
-      </c>
-      <c r="AW8" s="11">
-        <v>0</v>
-      </c>
-      <c r="AX8" s="11">
-        <v>0</v>
-      </c>
-      <c r="AY8" s="11">
-        <v>0</v>
-      </c>
-      <c r="AZ8" s="11">
-        <v>0</v>
-      </c>
-      <c r="BA8" s="11">
+      <c r="AJ8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AK8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AP8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AQ8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AS8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AT8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AU8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AV8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AW8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AX8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AY8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AZ8" s="10">
+        <v>0</v>
+      </c>
+      <c r="BA8" s="10">
         <v>0</v>
       </c>
     </row>
@@ -4799,64 +4798,64 @@
       <c r="AG9" s="10">
         <v>0</v>
       </c>
-      <c r="AH9" s="11">
+      <c r="AH9" s="10">
         <v>0</v>
       </c>
       <c r="AI9" s="10">
         <v>0</v>
       </c>
-      <c r="AJ9" s="11">
-        <v>0</v>
-      </c>
-      <c r="AK9" s="11">
-        <v>0</v>
-      </c>
-      <c r="AL9" s="11">
-        <v>0</v>
-      </c>
-      <c r="AM9" s="11">
-        <v>0</v>
-      </c>
-      <c r="AN9" s="11">
-        <v>0</v>
-      </c>
-      <c r="AO9" s="11">
-        <v>0</v>
-      </c>
-      <c r="AP9" s="11">
-        <v>0</v>
-      </c>
-      <c r="AQ9" s="11">
-        <v>0</v>
-      </c>
-      <c r="AR9" s="11">
-        <v>0</v>
-      </c>
-      <c r="AS9" s="11">
-        <v>0</v>
-      </c>
-      <c r="AT9" s="11">
-        <v>0</v>
-      </c>
-      <c r="AU9" s="11">
-        <v>0</v>
-      </c>
-      <c r="AV9" s="11">
-        <v>0</v>
-      </c>
-      <c r="AW9" s="11">
-        <v>0</v>
-      </c>
-      <c r="AX9" s="11">
-        <v>0</v>
-      </c>
-      <c r="AY9" s="11">
-        <v>0</v>
-      </c>
-      <c r="AZ9" s="11">
-        <v>0</v>
-      </c>
-      <c r="BA9" s="11">
+      <c r="AJ9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AK9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AP9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AQ9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AS9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AT9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AU9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AV9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AW9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AX9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AY9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AZ9" s="10">
+        <v>0</v>
+      </c>
+      <c r="BA9" s="10">
         <v>0</v>
       </c>
     </row>
@@ -4960,64 +4959,64 @@
       <c r="AG10" s="10">
         <v>0</v>
       </c>
-      <c r="AH10" s="11">
+      <c r="AH10" s="10">
         <v>0</v>
       </c>
       <c r="AI10" s="10">
         <v>0</v>
       </c>
-      <c r="AJ10" s="11">
-        <v>0</v>
-      </c>
-      <c r="AK10" s="11">
-        <v>0</v>
-      </c>
-      <c r="AL10" s="11">
-        <v>0</v>
-      </c>
-      <c r="AM10" s="11">
-        <v>0</v>
-      </c>
-      <c r="AN10" s="11">
-        <v>0</v>
-      </c>
-      <c r="AO10" s="11">
-        <v>0</v>
-      </c>
-      <c r="AP10" s="11">
-        <v>0</v>
-      </c>
-      <c r="AQ10" s="11">
-        <v>0</v>
-      </c>
-      <c r="AR10" s="11">
-        <v>0</v>
-      </c>
-      <c r="AS10" s="11">
-        <v>0</v>
-      </c>
-      <c r="AT10" s="11">
-        <v>0</v>
-      </c>
-      <c r="AU10" s="11">
-        <v>0</v>
-      </c>
-      <c r="AV10" s="11">
-        <v>0</v>
-      </c>
-      <c r="AW10" s="11">
-        <v>0</v>
-      </c>
-      <c r="AX10" s="11">
-        <v>0</v>
-      </c>
-      <c r="AY10" s="11">
-        <v>0</v>
-      </c>
-      <c r="AZ10" s="11">
-        <v>0</v>
-      </c>
-      <c r="BA10" s="11">
+      <c r="AJ10" s="10">
+        <v>0</v>
+      </c>
+      <c r="AK10" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL10" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM10" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN10" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO10" s="10">
+        <v>0</v>
+      </c>
+      <c r="AP10" s="10">
+        <v>0</v>
+      </c>
+      <c r="AQ10" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR10" s="10">
+        <v>0</v>
+      </c>
+      <c r="AS10" s="10">
+        <v>0</v>
+      </c>
+      <c r="AT10" s="10">
+        <v>0</v>
+      </c>
+      <c r="AU10" s="10">
+        <v>0</v>
+      </c>
+      <c r="AV10" s="10">
+        <v>0</v>
+      </c>
+      <c r="AW10" s="10">
+        <v>0</v>
+      </c>
+      <c r="AX10" s="10">
+        <v>0</v>
+      </c>
+      <c r="AY10" s="10">
+        <v>0</v>
+      </c>
+      <c r="AZ10" s="10">
+        <v>0</v>
+      </c>
+      <c r="BA10" s="10">
         <v>0</v>
       </c>
     </row>
@@ -5121,64 +5120,64 @@
       <c r="AG11" s="10">
         <v>0</v>
       </c>
-      <c r="AH11" s="11">
+      <c r="AH11" s="10">
         <v>0</v>
       </c>
       <c r="AI11" s="10">
         <v>0</v>
       </c>
-      <c r="AJ11" s="11">
-        <v>0</v>
-      </c>
-      <c r="AK11" s="11">
-        <v>0</v>
-      </c>
-      <c r="AL11" s="11">
-        <v>0</v>
-      </c>
-      <c r="AM11" s="11">
-        <v>0</v>
-      </c>
-      <c r="AN11" s="11">
-        <v>0</v>
-      </c>
-      <c r="AO11" s="11">
-        <v>0</v>
-      </c>
-      <c r="AP11" s="11">
-        <v>0</v>
-      </c>
-      <c r="AQ11" s="11">
-        <v>0</v>
-      </c>
-      <c r="AR11" s="11">
-        <v>0</v>
-      </c>
-      <c r="AS11" s="11">
-        <v>0</v>
-      </c>
-      <c r="AT11" s="11">
-        <v>0</v>
-      </c>
-      <c r="AU11" s="11">
-        <v>0</v>
-      </c>
-      <c r="AV11" s="11">
-        <v>0</v>
-      </c>
-      <c r="AW11" s="11">
-        <v>0</v>
-      </c>
-      <c r="AX11" s="11">
-        <v>0</v>
-      </c>
-      <c r="AY11" s="11">
-        <v>0</v>
-      </c>
-      <c r="AZ11" s="11">
-        <v>0</v>
-      </c>
-      <c r="BA11" s="11">
+      <c r="AJ11" s="10">
+        <v>0</v>
+      </c>
+      <c r="AK11" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL11" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM11" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN11" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO11" s="10">
+        <v>0</v>
+      </c>
+      <c r="AP11" s="10">
+        <v>0</v>
+      </c>
+      <c r="AQ11" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR11" s="10">
+        <v>0</v>
+      </c>
+      <c r="AS11" s="10">
+        <v>0</v>
+      </c>
+      <c r="AT11" s="10">
+        <v>0</v>
+      </c>
+      <c r="AU11" s="10">
+        <v>0</v>
+      </c>
+      <c r="AV11" s="10">
+        <v>0</v>
+      </c>
+      <c r="AW11" s="10">
+        <v>0</v>
+      </c>
+      <c r="AX11" s="10">
+        <v>0</v>
+      </c>
+      <c r="AY11" s="10">
+        <v>0</v>
+      </c>
+      <c r="AZ11" s="10">
+        <v>0</v>
+      </c>
+      <c r="BA11" s="10">
         <v>0</v>
       </c>
     </row>
@@ -5282,64 +5281,64 @@
       <c r="AG12" s="10">
         <v>0</v>
       </c>
-      <c r="AH12" s="11">
+      <c r="AH12" s="10">
         <v>0</v>
       </c>
       <c r="AI12" s="10">
         <v>0</v>
       </c>
-      <c r="AJ12" s="11">
-        <v>0</v>
-      </c>
-      <c r="AK12" s="11">
-        <v>0</v>
-      </c>
-      <c r="AL12" s="11">
-        <v>0</v>
-      </c>
-      <c r="AM12" s="11">
-        <v>0</v>
-      </c>
-      <c r="AN12" s="11">
-        <v>0</v>
-      </c>
-      <c r="AO12" s="11">
-        <v>0</v>
-      </c>
-      <c r="AP12" s="11">
-        <v>0</v>
-      </c>
-      <c r="AQ12" s="11">
-        <v>0</v>
-      </c>
-      <c r="AR12" s="11">
-        <v>0</v>
-      </c>
-      <c r="AS12" s="11">
-        <v>0</v>
-      </c>
-      <c r="AT12" s="11">
-        <v>0</v>
-      </c>
-      <c r="AU12" s="11">
-        <v>0</v>
-      </c>
-      <c r="AV12" s="11">
-        <v>0</v>
-      </c>
-      <c r="AW12" s="11">
-        <v>0</v>
-      </c>
-      <c r="AX12" s="11">
-        <v>0</v>
-      </c>
-      <c r="AY12" s="11">
-        <v>0</v>
-      </c>
-      <c r="AZ12" s="11">
-        <v>0</v>
-      </c>
-      <c r="BA12" s="11">
+      <c r="AJ12" s="10">
+        <v>0</v>
+      </c>
+      <c r="AK12" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL12" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM12" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN12" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO12" s="10">
+        <v>0</v>
+      </c>
+      <c r="AP12" s="10">
+        <v>0</v>
+      </c>
+      <c r="AQ12" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR12" s="10">
+        <v>0</v>
+      </c>
+      <c r="AS12" s="10">
+        <v>0</v>
+      </c>
+      <c r="AT12" s="10">
+        <v>0</v>
+      </c>
+      <c r="AU12" s="10">
+        <v>0</v>
+      </c>
+      <c r="AV12" s="10">
+        <v>0</v>
+      </c>
+      <c r="AW12" s="10">
+        <v>0</v>
+      </c>
+      <c r="AX12" s="10">
+        <v>0</v>
+      </c>
+      <c r="AY12" s="10">
+        <v>0</v>
+      </c>
+      <c r="AZ12" s="10">
+        <v>0</v>
+      </c>
+      <c r="BA12" s="10">
         <v>0</v>
       </c>
     </row>
@@ -5443,64 +5442,64 @@
       <c r="AG13" s="10">
         <v>0</v>
       </c>
-      <c r="AH13" s="11">
+      <c r="AH13" s="10">
         <v>0</v>
       </c>
       <c r="AI13" s="10">
         <v>0</v>
       </c>
-      <c r="AJ13" s="11">
-        <v>0</v>
-      </c>
-      <c r="AK13" s="11">
-        <v>0</v>
-      </c>
-      <c r="AL13" s="11">
-        <v>0</v>
-      </c>
-      <c r="AM13" s="11">
-        <v>0</v>
-      </c>
-      <c r="AN13" s="11">
-        <v>0</v>
-      </c>
-      <c r="AO13" s="11">
-        <v>0</v>
-      </c>
-      <c r="AP13" s="11">
-        <v>0</v>
-      </c>
-      <c r="AQ13" s="11">
-        <v>0</v>
-      </c>
-      <c r="AR13" s="11">
-        <v>0</v>
-      </c>
-      <c r="AS13" s="11">
-        <v>0</v>
-      </c>
-      <c r="AT13" s="11">
-        <v>0</v>
-      </c>
-      <c r="AU13" s="11">
-        <v>0</v>
-      </c>
-      <c r="AV13" s="11">
-        <v>0</v>
-      </c>
-      <c r="AW13" s="11">
-        <v>0</v>
-      </c>
-      <c r="AX13" s="11">
-        <v>0</v>
-      </c>
-      <c r="AY13" s="11">
-        <v>0</v>
-      </c>
-      <c r="AZ13" s="11">
-        <v>0</v>
-      </c>
-      <c r="BA13" s="11">
+      <c r="AJ13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AP13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AQ13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AS13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AT13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AU13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AV13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AW13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AX13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AY13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AZ13" s="10">
+        <v>0</v>
+      </c>
+      <c r="BA13" s="10">
         <v>0</v>
       </c>
     </row>
@@ -5604,64 +5603,64 @@
       <c r="AG14" s="10">
         <v>0</v>
       </c>
-      <c r="AH14" s="11">
+      <c r="AH14" s="10">
         <v>0</v>
       </c>
       <c r="AI14" s="10">
         <v>0</v>
       </c>
-      <c r="AJ14" s="11">
-        <v>0</v>
-      </c>
-      <c r="AK14" s="11">
-        <v>0</v>
-      </c>
-      <c r="AL14" s="11">
-        <v>0</v>
-      </c>
-      <c r="AM14" s="11">
-        <v>0</v>
-      </c>
-      <c r="AN14" s="11">
-        <v>0</v>
-      </c>
-      <c r="AO14" s="11">
-        <v>0</v>
-      </c>
-      <c r="AP14" s="11">
-        <v>0</v>
-      </c>
-      <c r="AQ14" s="11">
-        <v>0</v>
-      </c>
-      <c r="AR14" s="11">
-        <v>0</v>
-      </c>
-      <c r="AS14" s="11">
-        <v>0</v>
-      </c>
-      <c r="AT14" s="11">
-        <v>0</v>
-      </c>
-      <c r="AU14" s="11">
-        <v>0</v>
-      </c>
-      <c r="AV14" s="11">
-        <v>0</v>
-      </c>
-      <c r="AW14" s="11">
-        <v>0</v>
-      </c>
-      <c r="AX14" s="11">
-        <v>0</v>
-      </c>
-      <c r="AY14" s="11">
-        <v>0</v>
-      </c>
-      <c r="AZ14" s="11">
-        <v>0</v>
-      </c>
-      <c r="BA14" s="11">
+      <c r="AJ14" s="10">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM14" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN14" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO14" s="10">
+        <v>0</v>
+      </c>
+      <c r="AP14" s="10">
+        <v>0</v>
+      </c>
+      <c r="AQ14" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR14" s="10">
+        <v>0</v>
+      </c>
+      <c r="AS14" s="10">
+        <v>0</v>
+      </c>
+      <c r="AT14" s="10">
+        <v>0</v>
+      </c>
+      <c r="AU14" s="10">
+        <v>0</v>
+      </c>
+      <c r="AV14" s="10">
+        <v>0</v>
+      </c>
+      <c r="AW14" s="10">
+        <v>0</v>
+      </c>
+      <c r="AX14" s="10">
+        <v>0</v>
+      </c>
+      <c r="AY14" s="10">
+        <v>0</v>
+      </c>
+      <c r="AZ14" s="10">
+        <v>0</v>
+      </c>
+      <c r="BA14" s="10">
         <v>0</v>
       </c>
     </row>
@@ -5765,64 +5764,64 @@
       <c r="AG15" s="10">
         <v>0</v>
       </c>
-      <c r="AH15" s="11">
+      <c r="AH15" s="10">
         <v>0</v>
       </c>
       <c r="AI15" s="10">
         <v>0</v>
       </c>
-      <c r="AJ15" s="11">
-        <v>0</v>
-      </c>
-      <c r="AK15" s="11">
-        <v>0</v>
-      </c>
-      <c r="AL15" s="11">
-        <v>0</v>
-      </c>
-      <c r="AM15" s="11">
-        <v>0</v>
-      </c>
-      <c r="AN15" s="11">
-        <v>0</v>
-      </c>
-      <c r="AO15" s="11">
-        <v>0</v>
-      </c>
-      <c r="AP15" s="11">
-        <v>0</v>
-      </c>
-      <c r="AQ15" s="11">
-        <v>0</v>
-      </c>
-      <c r="AR15" s="11">
-        <v>0</v>
-      </c>
-      <c r="AS15" s="11">
-        <v>0</v>
-      </c>
-      <c r="AT15" s="11">
-        <v>0</v>
-      </c>
-      <c r="AU15" s="11">
-        <v>0</v>
-      </c>
-      <c r="AV15" s="11">
-        <v>0</v>
-      </c>
-      <c r="AW15" s="11">
-        <v>0</v>
-      </c>
-      <c r="AX15" s="11">
-        <v>0</v>
-      </c>
-      <c r="AY15" s="11">
-        <v>0</v>
-      </c>
-      <c r="AZ15" s="11">
-        <v>0</v>
-      </c>
-      <c r="BA15" s="11">
+      <c r="AJ15" s="10">
+        <v>0</v>
+      </c>
+      <c r="AK15" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL15" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM15" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN15" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO15" s="10">
+        <v>0</v>
+      </c>
+      <c r="AP15" s="10">
+        <v>0</v>
+      </c>
+      <c r="AQ15" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR15" s="10">
+        <v>0</v>
+      </c>
+      <c r="AS15" s="10">
+        <v>0</v>
+      </c>
+      <c r="AT15" s="10">
+        <v>0</v>
+      </c>
+      <c r="AU15" s="10">
+        <v>0</v>
+      </c>
+      <c r="AV15" s="10">
+        <v>0</v>
+      </c>
+      <c r="AW15" s="10">
+        <v>0</v>
+      </c>
+      <c r="AX15" s="10">
+        <v>0</v>
+      </c>
+      <c r="AY15" s="10">
+        <v>0</v>
+      </c>
+      <c r="AZ15" s="10">
+        <v>0</v>
+      </c>
+      <c r="BA15" s="10">
         <v>0</v>
       </c>
     </row>
@@ -5926,64 +5925,64 @@
       <c r="AG16" s="10">
         <v>0</v>
       </c>
-      <c r="AH16" s="11">
+      <c r="AH16" s="10">
         <v>0</v>
       </c>
       <c r="AI16" s="10">
         <v>0</v>
       </c>
-      <c r="AJ16" s="11">
-        <v>0</v>
-      </c>
-      <c r="AK16" s="11">
-        <v>0</v>
-      </c>
-      <c r="AL16" s="11">
-        <v>0</v>
-      </c>
-      <c r="AM16" s="11">
-        <v>0</v>
-      </c>
-      <c r="AN16" s="11">
-        <v>0</v>
-      </c>
-      <c r="AO16" s="11">
-        <v>0</v>
-      </c>
-      <c r="AP16" s="11">
-        <v>0</v>
-      </c>
-      <c r="AQ16" s="11">
-        <v>0</v>
-      </c>
-      <c r="AR16" s="11">
-        <v>0</v>
-      </c>
-      <c r="AS16" s="11">
-        <v>0</v>
-      </c>
-      <c r="AT16" s="11">
-        <v>0</v>
-      </c>
-      <c r="AU16" s="11">
-        <v>0</v>
-      </c>
-      <c r="AV16" s="11">
-        <v>0</v>
-      </c>
-      <c r="AW16" s="11">
-        <v>0</v>
-      </c>
-      <c r="AX16" s="11">
-        <v>0</v>
-      </c>
-      <c r="AY16" s="11">
-        <v>0</v>
-      </c>
-      <c r="AZ16" s="11">
-        <v>0</v>
-      </c>
-      <c r="BA16" s="11">
+      <c r="AJ16" s="10">
+        <v>0</v>
+      </c>
+      <c r="AK16" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL16" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM16" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN16" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO16" s="10">
+        <v>0</v>
+      </c>
+      <c r="AP16" s="10">
+        <v>0</v>
+      </c>
+      <c r="AQ16" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR16" s="10">
+        <v>0</v>
+      </c>
+      <c r="AS16" s="10">
+        <v>0</v>
+      </c>
+      <c r="AT16" s="10">
+        <v>0</v>
+      </c>
+      <c r="AU16" s="10">
+        <v>0</v>
+      </c>
+      <c r="AV16" s="10">
+        <v>0</v>
+      </c>
+      <c r="AW16" s="10">
+        <v>0</v>
+      </c>
+      <c r="AX16" s="10">
+        <v>0</v>
+      </c>
+      <c r="AY16" s="10">
+        <v>0</v>
+      </c>
+      <c r="AZ16" s="10">
+        <v>0</v>
+      </c>
+      <c r="BA16" s="10">
         <v>0</v>
       </c>
     </row>
@@ -6087,64 +6086,64 @@
       <c r="AG17" s="10">
         <v>0</v>
       </c>
-      <c r="AH17" s="11">
+      <c r="AH17" s="10">
         <v>0</v>
       </c>
       <c r="AI17" s="10">
         <v>0</v>
       </c>
-      <c r="AJ17" s="11">
-        <v>0</v>
-      </c>
-      <c r="AK17" s="11">
-        <v>0</v>
-      </c>
-      <c r="AL17" s="11">
-        <v>0</v>
-      </c>
-      <c r="AM17" s="11">
-        <v>0</v>
-      </c>
-      <c r="AN17" s="11">
-        <v>0</v>
-      </c>
-      <c r="AO17" s="11">
-        <v>0</v>
-      </c>
-      <c r="AP17" s="11">
-        <v>0</v>
-      </c>
-      <c r="AQ17" s="11">
-        <v>0</v>
-      </c>
-      <c r="AR17" s="11">
-        <v>0</v>
-      </c>
-      <c r="AS17" s="11">
-        <v>0</v>
-      </c>
-      <c r="AT17" s="11">
-        <v>0</v>
-      </c>
-      <c r="AU17" s="11">
-        <v>0</v>
-      </c>
-      <c r="AV17" s="11">
-        <v>0</v>
-      </c>
-      <c r="AW17" s="11">
-        <v>0</v>
-      </c>
-      <c r="AX17" s="11">
-        <v>0</v>
-      </c>
-      <c r="AY17" s="11">
-        <v>0</v>
-      </c>
-      <c r="AZ17" s="11">
-        <v>0</v>
-      </c>
-      <c r="BA17" s="11">
+      <c r="AJ17" s="10">
+        <v>0</v>
+      </c>
+      <c r="AK17" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL17" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM17" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN17" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO17" s="10">
+        <v>0</v>
+      </c>
+      <c r="AP17" s="10">
+        <v>0</v>
+      </c>
+      <c r="AQ17" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR17" s="10">
+        <v>0</v>
+      </c>
+      <c r="AS17" s="10">
+        <v>0</v>
+      </c>
+      <c r="AT17" s="10">
+        <v>0</v>
+      </c>
+      <c r="AU17" s="10">
+        <v>0</v>
+      </c>
+      <c r="AV17" s="10">
+        <v>0</v>
+      </c>
+      <c r="AW17" s="10">
+        <v>0</v>
+      </c>
+      <c r="AX17" s="10">
+        <v>0</v>
+      </c>
+      <c r="AY17" s="10">
+        <v>0</v>
+      </c>
+      <c r="AZ17" s="10">
+        <v>0</v>
+      </c>
+      <c r="BA17" s="10">
         <v>0</v>
       </c>
     </row>

--- a/InputData/elec/CRbQ/Cap Retirements before Quantization.xlsx
+++ b/InputData/elec/CRbQ/Cap Retirements before Quantization.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11027"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Postdoc Projects/eps-indonesia-cpl/InputData/elec/CRbQ/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mary Francis Swint\Vensim\eps-indonesia\InputData\elec\CRbQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE139A42-4913-6D4C-891D-6F30696E1BAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A437562F-6618-45B7-B12B-C00C280F5E2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21360" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="BCRBQ_IDN" sheetId="2" r:id="rId2"/>
-    <sheet name="CRbQ" sheetId="3" r:id="rId3"/>
+    <sheet name="BCRbQ" sheetId="4" r:id="rId3"/>
+    <sheet name="CRbQ" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="40">
   <si>
     <t>CRbQ Capacity Retirements before Quantization</t>
   </si>
@@ -164,7 +165,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -185,6 +186,14 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -218,7 +227,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -238,6 +247,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="11" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -454,20 +466,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B1000"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.1640625" customWidth="1"/>
+    <col min="1" max="1" width="20.140625" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="26" width="8.6640625" customWidth="1"/>
+    <col min="3" max="26" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="3" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -475,1088 +487,1088 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="3"/>
     </row>
-    <row r="9" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B9" s="3"/>
     </row>
-    <row r="10" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
     </row>
-    <row r="14" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
     </row>
-    <row r="18" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="26" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
     </row>
-    <row r="27" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="28" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="30" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="31" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="34" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="36" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="37" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="38" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="39" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="40" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="41" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="42" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="43" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="44" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="46" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="47" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="48" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="49" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="50" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="51" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="54" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="55" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="56" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="57" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="58" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="59" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="60" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="61" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="62" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="63" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="64" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="65" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="66" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="67" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="68" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="69" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="70" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="71" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="72" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="73" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="74" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="75" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="76" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="77" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="78" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="79" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="80" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="81" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="82" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="83" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="84" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="85" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="86" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="87" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="88" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="89" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="90" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="91" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="92" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="93" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="94" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="95" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="96" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="97" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="98" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="99" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="100" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="101" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="102" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="103" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="104" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="105" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="106" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="107" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="108" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="109" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="110" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="111" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="112" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="113" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="114" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="115" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="116" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="117" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="118" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="119" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="120" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="121" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="122" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="123" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="124" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="125" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="126" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="127" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="128" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="129" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="130" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="131" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="132" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="133" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="134" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="135" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="136" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="137" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="138" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="139" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="140" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="141" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="142" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="143" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="144" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="145" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="146" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="147" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="148" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="149" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="150" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="151" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="152" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="153" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="154" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="155" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="156" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="157" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="158" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="159" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="160" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="161" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="162" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="163" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="164" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="165" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="166" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="167" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="168" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="169" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="170" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="171" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="172" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="173" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="174" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="175" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="176" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="177" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="178" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="179" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="180" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="181" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="182" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="183" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="184" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="185" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="186" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="187" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="188" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="189" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="190" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="191" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="192" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="193" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="194" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="195" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="196" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="197" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="198" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="199" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="200" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="201" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="202" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="203" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="204" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="205" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="206" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="207" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="208" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="209" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="210" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="211" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="212" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="213" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="214" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="215" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="216" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="217" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="218" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="219" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="220" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="221" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="222" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="223" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="224" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="225" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="226" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="227" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="228" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="229" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="230" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="231" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="232" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="233" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="234" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="235" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="236" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="237" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="238" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="239" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="240" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="241" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="242" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="243" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="244" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="245" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="246" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="247" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="248" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="249" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="250" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="251" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="252" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="253" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="254" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="255" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="256" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="257" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="258" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="259" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="260" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="261" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="262" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="263" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="264" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="265" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="266" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="267" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="268" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="269" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="270" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="271" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="272" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="273" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="274" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="275" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="276" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="277" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="278" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="279" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="280" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="281" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="282" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="283" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="284" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="285" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="286" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="287" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="288" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="289" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="290" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="291" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="292" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="293" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="294" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="295" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="296" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="297" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="298" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="299" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="300" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="301" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="302" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="303" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="304" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="305" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="306" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="307" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="308" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="309" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="310" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="311" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="312" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="313" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="314" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="315" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="316" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="317" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="318" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="319" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="320" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="321" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="322" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="323" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="324" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="325" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="326" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="327" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="328" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="329" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="330" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="331" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="332" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="333" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="334" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="335" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="336" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="337" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="338" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="339" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="340" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="341" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="342" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="343" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="344" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="345" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="346" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="347" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="348" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="349" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="350" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="351" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="352" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="353" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="354" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="355" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="356" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="357" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="358" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="359" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="360" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="361" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="362" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="363" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="364" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="365" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="366" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="367" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="368" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="369" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="370" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="371" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="372" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="373" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="374" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="375" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="376" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="377" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="378" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="379" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="380" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="381" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="382" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="383" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="384" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="385" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="386" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="387" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="388" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="389" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="390" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="391" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="392" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="393" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="394" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="395" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="396" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="397" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="398" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="399" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="400" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="401" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="402" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="403" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="404" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="405" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="406" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="407" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="408" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="409" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="410" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="411" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="412" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="413" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="414" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="415" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="416" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="417" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="418" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="419" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="420" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="421" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="422" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="423" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="424" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="425" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="426" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="427" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="428" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="429" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="430" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="431" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="432" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="433" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="434" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="435" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="436" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="437" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="438" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="439" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="440" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="441" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="442" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="443" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="444" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="445" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="446" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="447" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="448" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="449" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="450" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="451" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="452" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="453" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="454" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="455" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="456" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="457" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="458" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="459" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="460" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="461" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="462" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="463" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="464" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="465" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="466" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="467" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="468" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="469" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="470" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="471" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="472" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="473" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="474" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="475" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="476" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="477" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="478" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="479" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="480" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="481" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="482" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="483" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="484" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="485" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="486" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="487" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="488" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="489" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="490" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="491" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="492" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="493" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="494" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="495" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="496" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="497" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="498" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="499" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="500" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="501" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="502" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="503" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="504" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="505" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="506" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="507" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="508" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="509" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="510" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="511" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="512" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="513" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="514" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="515" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="516" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="517" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="518" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="519" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="520" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="521" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="522" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="523" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="524" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="525" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="526" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="527" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="528" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="529" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="530" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="531" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="532" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="533" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="534" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="535" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="536" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="537" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="538" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="539" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="540" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="541" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="542" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="543" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="544" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="545" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="546" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="547" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="548" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="549" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="550" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="551" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="552" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="553" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="554" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="555" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="556" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="557" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="558" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="559" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="560" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="561" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="562" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="563" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="564" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="565" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="566" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="567" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="568" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="569" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="570" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="571" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="572" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="573" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="574" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="575" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="576" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="577" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="578" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="579" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="580" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="581" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="582" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="583" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="584" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="585" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="586" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="587" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="588" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="589" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="590" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="591" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="592" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="593" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="594" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="595" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="596" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="597" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="598" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="599" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="600" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="601" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="602" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="603" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="604" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="605" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="606" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="607" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="608" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="609" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="610" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="611" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="612" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="613" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="614" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="615" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="616" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="617" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="618" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="619" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="620" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="621" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="622" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="623" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="624" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="625" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="626" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="627" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="628" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="629" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="630" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="631" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="632" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="633" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="634" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="635" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="636" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="637" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="638" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="639" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="640" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="641" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="642" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="643" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="644" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="645" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="646" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="647" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="648" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="649" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="650" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="651" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="652" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="653" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="654" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="655" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="656" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="657" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="658" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="659" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="660" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="661" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="662" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="663" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="664" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="665" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="666" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="667" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="668" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="669" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="670" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="671" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="672" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="673" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="674" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="675" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="676" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="677" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="678" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="679" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="680" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="681" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="682" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="683" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="684" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="685" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="686" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="687" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="688" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="689" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="690" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="691" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="692" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="693" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="694" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="695" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="696" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="697" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="698" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="699" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="700" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="701" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="702" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="703" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="704" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="705" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="706" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="707" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="708" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="709" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="710" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="711" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="712" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="713" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="714" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="715" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="716" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="717" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="718" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="719" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="720" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="721" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="722" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="723" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="724" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="725" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="726" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="727" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="728" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="729" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="730" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="731" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="732" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="733" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="734" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="735" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="736" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="737" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="738" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="739" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="740" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="741" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="742" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="743" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="744" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="745" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="746" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="747" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="748" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="749" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="750" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="751" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="752" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="753" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="754" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="755" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="756" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="757" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="758" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="759" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="760" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="761" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="762" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="763" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="764" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="765" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="766" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="767" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="768" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="769" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="770" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="771" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="772" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="773" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="774" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="775" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="776" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="777" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="778" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="779" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="780" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="781" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="782" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="783" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="784" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="785" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="786" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="787" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="788" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="789" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="790" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="791" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="792" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="793" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="794" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="795" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="796" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="797" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="798" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="799" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="800" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="801" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="802" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="803" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="804" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="805" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="806" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="807" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="808" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="809" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="810" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="811" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="812" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="813" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="814" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="815" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="816" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="817" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="818" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="819" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="820" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="821" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="822" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="823" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="824" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="825" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="826" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="827" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="828" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="829" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="830" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="831" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="832" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="833" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="834" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="835" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="836" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="837" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="838" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="839" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="840" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="841" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="842" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="843" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="844" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="845" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="846" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="847" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="848" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="849" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="850" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="851" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="852" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="853" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="854" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="855" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="856" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="857" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="858" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="859" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="860" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="861" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="862" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="863" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="864" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="865" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="866" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="867" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="868" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="869" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="870" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="871" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="872" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="873" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="874" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="875" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="876" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="877" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="878" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="879" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="880" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="881" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="882" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="883" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="884" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="885" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="886" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="887" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="888" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="889" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="890" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="891" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="892" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="893" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="894" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="895" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="896" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="897" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="898" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="899" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="900" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="901" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="902" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="903" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="904" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="905" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="906" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="907" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="908" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="909" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="910" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="911" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="912" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="913" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="914" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="915" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="916" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="917" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="918" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="919" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="920" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="921" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="922" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="923" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="924" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="925" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="926" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="927" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="928" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="929" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="930" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="931" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="932" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="933" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="934" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="935" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="936" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="937" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="938" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="939" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="940" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="941" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="942" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="943" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="944" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="945" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="946" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="947" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="948" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="949" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="950" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="951" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="952" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="953" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="954" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="955" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="956" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="957" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="958" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="959" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="960" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="961" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="962" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="963" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="964" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="965" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="966" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="967" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="968" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="969" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="970" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="971" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="972" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="973" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="974" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="975" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="976" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="977" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="978" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="979" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="980" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="981" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="982" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="983" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="984" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="985" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="986" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="987" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="988" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="989" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="990" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="991" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="992" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="993" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="994" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="995" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="996" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="997" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="998" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="999" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1000" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="27" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="190" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="191" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="193" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="194" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="195" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="196" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="197" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="198" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="199" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="200" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="201" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="202" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="203" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="206" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="207" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="208" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="209" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="210" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="211" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="213" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="223" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="225" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="227" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="229" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="231" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="232" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="233" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="234" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="235" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="237" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="238" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="239" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="240" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="241" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="242" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="243" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="244" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="245" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="246" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="247" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="248" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="249" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="250" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="251" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="252" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="253" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="254" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="255" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="256" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="257" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="258" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="259" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="260" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="261" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="262" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="263" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="264" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="265" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="266" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="267" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="268" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="269" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="270" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="271" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="272" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="273" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="274" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="275" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="276" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="277" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="278" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="279" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="280" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="281" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="282" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="283" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="284" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="285" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="286" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="287" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="288" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="289" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="290" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="291" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="292" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="293" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="294" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="295" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="296" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="297" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="298" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="299" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="300" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="301" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="302" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="303" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="304" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="305" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="306" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="307" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="308" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="309" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="310" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="311" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="312" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="313" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="314" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="315" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="316" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="317" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="318" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="319" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="320" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="321" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="322" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="323" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="324" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="325" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="326" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="327" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="328" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="329" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="330" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="331" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="332" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="333" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="334" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="335" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="336" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="337" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="338" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="339" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="340" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="341" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="342" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="343" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="344" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="345" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="346" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="347" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="348" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="349" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="350" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="351" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="352" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="353" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="354" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="355" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="356" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="357" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="358" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="359" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="360" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="361" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="362" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="363" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="364" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="365" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="366" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="367" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="368" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="369" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="370" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="371" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="372" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="373" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="374" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="375" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="376" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="377" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="378" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="379" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="380" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="381" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="382" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="383" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="384" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="385" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="386" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="387" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="388" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="389" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="390" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="391" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="392" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="393" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="394" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="395" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="396" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="397" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="398" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="399" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="400" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="401" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="402" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="403" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="404" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="405" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="406" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="407" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="408" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="409" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="410" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="411" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="412" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="413" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="414" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="415" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="416" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="417" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="418" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="419" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="420" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="421" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="422" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="423" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="424" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="425" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="426" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="427" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="428" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="429" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="430" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="431" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="432" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="433" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="434" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="435" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="436" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="437" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="438" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="439" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="440" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="441" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="442" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="443" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="444" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="445" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="446" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="447" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="448" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="449" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="450" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="451" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="452" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="453" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="454" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="455" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="456" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="457" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="458" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="459" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="460" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="461" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="462" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="463" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="464" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="465" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="466" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="467" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="468" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="469" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="470" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="471" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="472" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="473" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="474" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="475" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="476" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="477" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="478" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="479" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="480" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="481" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="482" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="483" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="484" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="485" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="486" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="487" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="488" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="489" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="490" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="491" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="492" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="493" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="494" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="495" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="496" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="497" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="498" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="499" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="500" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="501" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="502" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="503" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="504" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="505" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="506" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="507" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="508" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="509" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="510" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="511" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="512" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="513" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="514" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="515" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="516" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="517" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="518" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="519" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="520" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="521" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="522" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="523" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="524" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="525" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="526" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="527" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="528" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="529" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="530" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="531" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="532" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="533" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="534" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="535" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="536" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="537" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="538" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="539" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="540" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="541" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="542" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="543" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="544" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="545" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="546" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="547" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="548" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="549" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="550" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="551" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="552" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="553" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="554" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="555" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="556" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="557" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="558" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="559" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="560" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="561" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="562" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="563" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="564" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="565" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="566" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="567" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="568" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="569" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="570" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="571" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="572" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="573" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="574" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="575" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="576" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="577" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="578" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="579" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="580" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="581" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="582" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="583" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="584" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="585" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="586" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="587" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="588" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="589" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="590" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="591" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="592" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="593" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="594" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="595" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="596" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="597" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="598" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="599" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="600" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="601" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="602" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="603" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="604" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="605" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="606" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="607" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="608" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="609" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="610" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="611" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="612" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="613" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="614" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="615" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="616" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="617" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="618" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="619" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="620" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="621" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="622" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="623" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="624" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="625" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="626" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="627" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="628" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="629" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="630" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="631" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="632" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="633" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="634" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="635" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="636" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="637" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="638" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="639" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="640" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="641" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="642" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="643" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="644" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="645" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="646" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="647" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="648" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="649" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="650" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="651" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="652" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="653" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="654" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="655" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="656" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="657" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="658" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="659" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="660" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="661" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="662" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="663" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="664" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="665" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="666" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="667" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="668" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="669" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="670" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="671" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="672" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="673" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="674" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="675" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="676" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="677" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="678" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="679" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="680" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="681" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="682" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="683" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="684" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="685" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="686" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="687" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="688" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="689" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="690" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="691" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="692" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="693" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="694" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="695" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="696" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="697" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="698" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="699" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="700" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="701" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="702" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="703" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="704" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="705" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="706" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="707" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="708" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="709" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="710" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="711" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="712" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="713" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="714" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="715" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="716" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="717" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="718" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="719" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="720" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="721" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="722" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="723" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="724" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="725" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="726" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="727" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="728" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="729" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="730" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="731" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="732" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="733" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="734" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="735" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="736" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="737" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="738" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="739" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="740" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="741" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="742" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="743" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="744" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="745" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="746" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="747" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="748" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="749" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="750" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="751" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="752" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="753" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="754" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="755" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="756" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="757" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="758" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="759" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="760" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="761" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="762" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="763" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="764" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="765" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="766" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="767" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="768" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="769" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="770" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="771" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="772" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="773" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="774" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="775" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="776" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="777" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="778" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="779" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="780" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="781" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="782" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="783" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="784" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="785" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="786" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="787" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="788" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="789" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="790" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="791" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="792" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="793" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="794" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="795" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="796" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="797" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="798" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="799" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="800" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="801" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="802" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="803" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="804" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="805" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="806" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="807" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="808" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="809" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="810" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="811" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="812" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="813" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="814" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="815" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="816" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="817" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="818" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="819" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="820" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="821" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="822" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="823" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="824" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="825" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="826" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="827" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="828" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="829" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="830" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="831" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="832" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="833" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="834" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="835" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="836" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="837" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="838" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="839" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="840" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="841" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="842" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="843" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="844" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="845" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="846" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="847" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="848" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="849" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="850" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="851" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="852" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="853" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="854" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="855" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="856" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="857" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="858" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="859" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="860" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="861" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="862" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="863" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="864" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="865" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="866" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="867" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="868" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="869" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="870" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="871" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="872" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="873" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="874" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="875" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="876" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="877" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="878" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="879" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="880" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="881" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="882" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="883" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="884" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="885" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="886" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="887" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="888" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="889" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="890" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="891" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="892" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="893" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="894" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="895" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="896" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="897" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="898" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="899" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="900" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="901" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="902" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="903" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="904" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="905" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="906" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="907" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="908" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="909" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="910" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="911" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="912" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="913" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="914" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="915" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="916" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="917" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="918" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="919" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="920" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="921" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="922" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="923" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="924" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="925" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="926" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="927" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="928" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="929" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="930" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="931" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="932" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="933" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="934" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="935" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="936" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="937" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="938" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="939" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="940" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="941" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="942" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="943" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="944" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="945" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="946" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="947" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="948" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="949" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="950" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="951" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="952" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="953" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="954" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="955" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="956" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="957" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="958" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="959" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="960" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="961" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="962" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="963" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="964" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="965" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="966" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="967" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="968" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="969" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="970" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="971" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="972" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="973" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="974" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="975" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="976" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="977" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="978" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="979" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="980" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="981" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="982" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="983" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="984" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="985" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="986" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="987" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="988" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="989" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="990" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="991" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="992" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="993" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="994" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="995" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="996" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="997" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="998" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="999" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1000" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="portrait"/>
@@ -1569,12 +1581,12 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AG18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.5" customWidth="1"/>
+    <col min="1" max="1" width="30.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>21</v>
       </c>
@@ -1675,7 +1687,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>22</v>
       </c>
@@ -1776,7 +1788,7 @@
         <v>14.499999999998636</v>
       </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>23</v>
       </c>
@@ -1877,7 +1889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>24</v>
       </c>
@@ -1978,7 +1990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>25</v>
       </c>
@@ -2079,7 +2091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>26</v>
       </c>
@@ -2180,7 +2192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>27</v>
       </c>
@@ -2281,7 +2293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>28</v>
       </c>
@@ -2382,7 +2394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>29</v>
       </c>
@@ -2483,7 +2495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>30</v>
       </c>
@@ -2584,7 +2596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>31</v>
       </c>
@@ -2685,7 +2697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>32</v>
       </c>
@@ -2786,7 +2798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>33</v>
       </c>
@@ -2887,7 +2899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
         <v>34</v>
       </c>
@@ -2988,7 +3000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
         <v>35</v>
       </c>
@@ -3089,7 +3101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
         <v>36</v>
       </c>
@@ -3190,7 +3202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
         <v>37</v>
       </c>
@@ -3291,7 +3303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
         <v>38</v>
       </c>
@@ -3398,19 +3410,2927 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{556013AF-EC51-F841-A600-B92BB7D8ABAE}">
+  <dimension ref="A1:BA18"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:53" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="11">
+        <v>2019</v>
+      </c>
+      <c r="C1" s="11">
+        <v>2020</v>
+      </c>
+      <c r="D1" s="11">
+        <v>2021</v>
+      </c>
+      <c r="E1" s="11">
+        <v>2022</v>
+      </c>
+      <c r="F1" s="11">
+        <v>2023</v>
+      </c>
+      <c r="G1" s="11">
+        <v>2024</v>
+      </c>
+      <c r="H1" s="11">
+        <v>2025</v>
+      </c>
+      <c r="I1" s="11">
+        <v>2026</v>
+      </c>
+      <c r="J1" s="11">
+        <v>2027</v>
+      </c>
+      <c r="K1" s="11">
+        <v>2028</v>
+      </c>
+      <c r="L1" s="11">
+        <v>2029</v>
+      </c>
+      <c r="M1" s="11">
+        <v>2030</v>
+      </c>
+      <c r="N1" s="11">
+        <v>2031</v>
+      </c>
+      <c r="O1" s="11">
+        <v>2032</v>
+      </c>
+      <c r="P1" s="11">
+        <v>2033</v>
+      </c>
+      <c r="Q1" s="11">
+        <v>2034</v>
+      </c>
+      <c r="R1" s="11">
+        <v>2035</v>
+      </c>
+      <c r="S1" s="11">
+        <v>2036</v>
+      </c>
+      <c r="T1" s="11">
+        <v>2037</v>
+      </c>
+      <c r="U1" s="11">
+        <v>2038</v>
+      </c>
+      <c r="V1" s="11">
+        <v>2039</v>
+      </c>
+      <c r="W1" s="11">
+        <v>2040</v>
+      </c>
+      <c r="X1" s="11">
+        <v>2041</v>
+      </c>
+      <c r="Y1" s="11">
+        <v>2042</v>
+      </c>
+      <c r="Z1" s="11">
+        <v>2043</v>
+      </c>
+      <c r="AA1" s="11">
+        <v>2044</v>
+      </c>
+      <c r="AB1" s="11">
+        <v>2045</v>
+      </c>
+      <c r="AC1" s="11">
+        <v>2046</v>
+      </c>
+      <c r="AD1" s="11">
+        <v>2047</v>
+      </c>
+      <c r="AE1" s="11">
+        <v>2048</v>
+      </c>
+      <c r="AF1" s="11">
+        <v>2049</v>
+      </c>
+      <c r="AG1" s="11">
+        <v>2050</v>
+      </c>
+      <c r="AH1" s="13">
+        <v>2051</v>
+      </c>
+      <c r="AI1" s="13">
+        <v>2052</v>
+      </c>
+      <c r="AJ1" s="13">
+        <v>2053</v>
+      </c>
+      <c r="AK1" s="13">
+        <v>2054</v>
+      </c>
+      <c r="AL1" s="13">
+        <v>2055</v>
+      </c>
+      <c r="AM1" s="13">
+        <v>2056</v>
+      </c>
+      <c r="AN1" s="13">
+        <v>2057</v>
+      </c>
+      <c r="AO1" s="13">
+        <v>2058</v>
+      </c>
+      <c r="AP1" s="13">
+        <v>2059</v>
+      </c>
+      <c r="AQ1" s="13">
+        <v>2060</v>
+      </c>
+      <c r="AR1" s="13">
+        <v>2061</v>
+      </c>
+      <c r="AS1" s="13">
+        <v>2062</v>
+      </c>
+      <c r="AT1" s="13">
+        <v>2063</v>
+      </c>
+      <c r="AU1" s="13">
+        <v>2064</v>
+      </c>
+      <c r="AV1" s="13">
+        <v>2065</v>
+      </c>
+      <c r="AW1" s="13">
+        <v>2066</v>
+      </c>
+      <c r="AX1" s="13">
+        <v>2067</v>
+      </c>
+      <c r="AY1" s="13">
+        <v>2068</v>
+      </c>
+      <c r="AZ1" s="13">
+        <v>2069</v>
+      </c>
+      <c r="BA1" s="13">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="2" spans="1:53" x14ac:dyDescent="0.25">
+      <c r="A2" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="12">
+        <v>157.14285714285714</v>
+      </c>
+      <c r="C2" s="12">
+        <v>157.14285714285714</v>
+      </c>
+      <c r="D2" s="12">
+        <v>157.14285714285714</v>
+      </c>
+      <c r="E2" s="12">
+        <v>157.14285714285714</v>
+      </c>
+      <c r="F2" s="12">
+        <v>157.14285714285714</v>
+      </c>
+      <c r="G2" s="12">
+        <v>157.14285714285714</v>
+      </c>
+      <c r="H2" s="12">
+        <v>157.14285714285714</v>
+      </c>
+      <c r="I2" s="12">
+        <v>200</v>
+      </c>
+      <c r="J2" s="12">
+        <v>200</v>
+      </c>
+      <c r="K2" s="12">
+        <v>200</v>
+      </c>
+      <c r="L2" s="12">
+        <v>200</v>
+      </c>
+      <c r="M2" s="12">
+        <v>200</v>
+      </c>
+      <c r="N2" s="12">
+        <v>0</v>
+      </c>
+      <c r="O2" s="12">
+        <v>0</v>
+      </c>
+      <c r="P2" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="12">
+        <v>0</v>
+      </c>
+      <c r="R2" s="12">
+        <v>0</v>
+      </c>
+      <c r="S2" s="12">
+        <v>0</v>
+      </c>
+      <c r="T2" s="12">
+        <v>0</v>
+      </c>
+      <c r="U2" s="12">
+        <v>0</v>
+      </c>
+      <c r="V2" s="12">
+        <v>0</v>
+      </c>
+      <c r="W2" s="12">
+        <v>0</v>
+      </c>
+      <c r="X2" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="12">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="12">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF2" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG2" s="12">
+        <v>0</v>
+      </c>
+      <c r="AH2" s="12">
+        <v>0</v>
+      </c>
+      <c r="AI2" s="12">
+        <v>0</v>
+      </c>
+      <c r="AJ2" s="12">
+        <v>0</v>
+      </c>
+      <c r="AK2" s="12">
+        <v>0</v>
+      </c>
+      <c r="AL2" s="12">
+        <v>0</v>
+      </c>
+      <c r="AM2" s="12">
+        <v>0</v>
+      </c>
+      <c r="AN2" s="12">
+        <v>0</v>
+      </c>
+      <c r="AO2" s="12">
+        <v>0</v>
+      </c>
+      <c r="AP2" s="12">
+        <v>0</v>
+      </c>
+      <c r="AQ2" s="12">
+        <v>0</v>
+      </c>
+      <c r="AR2" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS2" s="12">
+        <v>0</v>
+      </c>
+      <c r="AT2" s="12">
+        <v>0</v>
+      </c>
+      <c r="AU2" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV2" s="12">
+        <v>0</v>
+      </c>
+      <c r="AW2" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX2" s="12">
+        <v>0</v>
+      </c>
+      <c r="AY2" s="12">
+        <v>0</v>
+      </c>
+      <c r="AZ2" s="12">
+        <v>0</v>
+      </c>
+      <c r="BA2" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:53" x14ac:dyDescent="0.25">
+      <c r="A3" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="12">
+        <v>0</v>
+      </c>
+      <c r="C3" s="12">
+        <v>0</v>
+      </c>
+      <c r="D3" s="12">
+        <v>0</v>
+      </c>
+      <c r="E3" s="12">
+        <v>0</v>
+      </c>
+      <c r="F3" s="12">
+        <v>0</v>
+      </c>
+      <c r="G3" s="12">
+        <v>0</v>
+      </c>
+      <c r="H3" s="12">
+        <v>0</v>
+      </c>
+      <c r="I3" s="12">
+        <v>0</v>
+      </c>
+      <c r="J3" s="12">
+        <v>0</v>
+      </c>
+      <c r="K3" s="12">
+        <v>0</v>
+      </c>
+      <c r="L3" s="12">
+        <v>0</v>
+      </c>
+      <c r="M3" s="12">
+        <v>0</v>
+      </c>
+      <c r="N3" s="12">
+        <v>0</v>
+      </c>
+      <c r="O3" s="12">
+        <v>0</v>
+      </c>
+      <c r="P3" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="12">
+        <v>0</v>
+      </c>
+      <c r="R3" s="12">
+        <v>0</v>
+      </c>
+      <c r="S3" s="12">
+        <v>0</v>
+      </c>
+      <c r="T3" s="12">
+        <v>0</v>
+      </c>
+      <c r="U3" s="12">
+        <v>0</v>
+      </c>
+      <c r="V3" s="12">
+        <v>0</v>
+      </c>
+      <c r="W3" s="12">
+        <v>0</v>
+      </c>
+      <c r="X3" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="12">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="12">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF3" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="12">
+        <v>0</v>
+      </c>
+      <c r="AH3" s="12">
+        <v>0</v>
+      </c>
+      <c r="AI3" s="12">
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="12">
+        <v>0</v>
+      </c>
+      <c r="AK3" s="12">
+        <v>0</v>
+      </c>
+      <c r="AL3" s="12">
+        <v>0</v>
+      </c>
+      <c r="AM3" s="12">
+        <v>0</v>
+      </c>
+      <c r="AN3" s="12">
+        <v>0</v>
+      </c>
+      <c r="AO3" s="12">
+        <v>0</v>
+      </c>
+      <c r="AP3" s="12">
+        <v>0</v>
+      </c>
+      <c r="AQ3" s="12">
+        <v>0</v>
+      </c>
+      <c r="AR3" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS3" s="12">
+        <v>0</v>
+      </c>
+      <c r="AT3" s="12">
+        <v>0</v>
+      </c>
+      <c r="AU3" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV3" s="12">
+        <v>0</v>
+      </c>
+      <c r="AW3" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX3" s="12">
+        <v>0</v>
+      </c>
+      <c r="AY3" s="12">
+        <v>0</v>
+      </c>
+      <c r="AZ3" s="12">
+        <v>0</v>
+      </c>
+      <c r="BA3" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:53" x14ac:dyDescent="0.25">
+      <c r="A4" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="12">
+        <v>0</v>
+      </c>
+      <c r="C4" s="12">
+        <v>0</v>
+      </c>
+      <c r="D4" s="12">
+        <v>0</v>
+      </c>
+      <c r="E4" s="12">
+        <v>0</v>
+      </c>
+      <c r="F4" s="12">
+        <v>0</v>
+      </c>
+      <c r="G4" s="12">
+        <v>0</v>
+      </c>
+      <c r="H4" s="12">
+        <v>0</v>
+      </c>
+      <c r="I4" s="12">
+        <v>0</v>
+      </c>
+      <c r="J4" s="12">
+        <v>0</v>
+      </c>
+      <c r="K4" s="12">
+        <v>0</v>
+      </c>
+      <c r="L4" s="12">
+        <v>0</v>
+      </c>
+      <c r="M4" s="12">
+        <v>0</v>
+      </c>
+      <c r="N4" s="12">
+        <v>0</v>
+      </c>
+      <c r="O4" s="12">
+        <v>0</v>
+      </c>
+      <c r="P4" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="12">
+        <v>0</v>
+      </c>
+      <c r="R4" s="12">
+        <v>0</v>
+      </c>
+      <c r="S4" s="12">
+        <v>0</v>
+      </c>
+      <c r="T4" s="12">
+        <v>0</v>
+      </c>
+      <c r="U4" s="12">
+        <v>0</v>
+      </c>
+      <c r="V4" s="12">
+        <v>0</v>
+      </c>
+      <c r="W4" s="12">
+        <v>0</v>
+      </c>
+      <c r="X4" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="12">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="12">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF4" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG4" s="12">
+        <v>0</v>
+      </c>
+      <c r="AH4" s="12">
+        <v>0</v>
+      </c>
+      <c r="AI4" s="12">
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="12">
+        <v>0</v>
+      </c>
+      <c r="AK4" s="12">
+        <v>0</v>
+      </c>
+      <c r="AL4" s="12">
+        <v>0</v>
+      </c>
+      <c r="AM4" s="12">
+        <v>0</v>
+      </c>
+      <c r="AN4" s="12">
+        <v>0</v>
+      </c>
+      <c r="AO4" s="12">
+        <v>0</v>
+      </c>
+      <c r="AP4" s="12">
+        <v>0</v>
+      </c>
+      <c r="AQ4" s="12">
+        <v>0</v>
+      </c>
+      <c r="AR4" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS4" s="12">
+        <v>0</v>
+      </c>
+      <c r="AT4" s="12">
+        <v>0</v>
+      </c>
+      <c r="AU4" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV4" s="12">
+        <v>0</v>
+      </c>
+      <c r="AW4" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX4" s="12">
+        <v>0</v>
+      </c>
+      <c r="AY4" s="12">
+        <v>0</v>
+      </c>
+      <c r="AZ4" s="12">
+        <v>0</v>
+      </c>
+      <c r="BA4" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:53" x14ac:dyDescent="0.25">
+      <c r="A5" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="12">
+        <v>0</v>
+      </c>
+      <c r="C5" s="12">
+        <v>0</v>
+      </c>
+      <c r="D5" s="12">
+        <v>0</v>
+      </c>
+      <c r="E5" s="12">
+        <v>0</v>
+      </c>
+      <c r="F5" s="12">
+        <v>0</v>
+      </c>
+      <c r="G5" s="12">
+        <v>0</v>
+      </c>
+      <c r="H5" s="12">
+        <v>0</v>
+      </c>
+      <c r="I5" s="12">
+        <v>0</v>
+      </c>
+      <c r="J5" s="12">
+        <v>0</v>
+      </c>
+      <c r="K5" s="12">
+        <v>0</v>
+      </c>
+      <c r="L5" s="12">
+        <v>0</v>
+      </c>
+      <c r="M5" s="12">
+        <v>0</v>
+      </c>
+      <c r="N5" s="12">
+        <v>0</v>
+      </c>
+      <c r="O5" s="12">
+        <v>0</v>
+      </c>
+      <c r="P5" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="12">
+        <v>0</v>
+      </c>
+      <c r="R5" s="12">
+        <v>0</v>
+      </c>
+      <c r="S5" s="12">
+        <v>0</v>
+      </c>
+      <c r="T5" s="12">
+        <v>0</v>
+      </c>
+      <c r="U5" s="12">
+        <v>0</v>
+      </c>
+      <c r="V5" s="12">
+        <v>0</v>
+      </c>
+      <c r="W5" s="12">
+        <v>0</v>
+      </c>
+      <c r="X5" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="12">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="12">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF5" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG5" s="12">
+        <v>0</v>
+      </c>
+      <c r="AH5" s="12">
+        <v>0</v>
+      </c>
+      <c r="AI5" s="12">
+        <v>0</v>
+      </c>
+      <c r="AJ5" s="12">
+        <v>0</v>
+      </c>
+      <c r="AK5" s="12">
+        <v>0</v>
+      </c>
+      <c r="AL5" s="12">
+        <v>0</v>
+      </c>
+      <c r="AM5" s="12">
+        <v>0</v>
+      </c>
+      <c r="AN5" s="12">
+        <v>0</v>
+      </c>
+      <c r="AO5" s="12">
+        <v>0</v>
+      </c>
+      <c r="AP5" s="12">
+        <v>0</v>
+      </c>
+      <c r="AQ5" s="12">
+        <v>0</v>
+      </c>
+      <c r="AR5" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS5" s="12">
+        <v>0</v>
+      </c>
+      <c r="AT5" s="12">
+        <v>0</v>
+      </c>
+      <c r="AU5" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV5" s="12">
+        <v>0</v>
+      </c>
+      <c r="AW5" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX5" s="12">
+        <v>0</v>
+      </c>
+      <c r="AY5" s="12">
+        <v>0</v>
+      </c>
+      <c r="AZ5" s="12">
+        <v>0</v>
+      </c>
+      <c r="BA5" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:53" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="12">
+        <v>0</v>
+      </c>
+      <c r="C6" s="12">
+        <v>0</v>
+      </c>
+      <c r="D6" s="12">
+        <v>0</v>
+      </c>
+      <c r="E6" s="12">
+        <v>0</v>
+      </c>
+      <c r="F6" s="12">
+        <v>0</v>
+      </c>
+      <c r="G6" s="12">
+        <v>0</v>
+      </c>
+      <c r="H6" s="12">
+        <v>0</v>
+      </c>
+      <c r="I6" s="12">
+        <v>0</v>
+      </c>
+      <c r="J6" s="12">
+        <v>0</v>
+      </c>
+      <c r="K6" s="12">
+        <v>0</v>
+      </c>
+      <c r="L6" s="12">
+        <v>0</v>
+      </c>
+      <c r="M6" s="12">
+        <v>0</v>
+      </c>
+      <c r="N6" s="12">
+        <v>0</v>
+      </c>
+      <c r="O6" s="12">
+        <v>0</v>
+      </c>
+      <c r="P6" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="12">
+        <v>0</v>
+      </c>
+      <c r="R6" s="12">
+        <v>0</v>
+      </c>
+      <c r="S6" s="12">
+        <v>0</v>
+      </c>
+      <c r="T6" s="12">
+        <v>0</v>
+      </c>
+      <c r="U6" s="12">
+        <v>0</v>
+      </c>
+      <c r="V6" s="12">
+        <v>0</v>
+      </c>
+      <c r="W6" s="12">
+        <v>0</v>
+      </c>
+      <c r="X6" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="12">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="12">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="12">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="12">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="12">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="12">
+        <v>0</v>
+      </c>
+      <c r="AK6" s="12">
+        <v>0</v>
+      </c>
+      <c r="AL6" s="12">
+        <v>0</v>
+      </c>
+      <c r="AM6" s="12">
+        <v>0</v>
+      </c>
+      <c r="AN6" s="12">
+        <v>0</v>
+      </c>
+      <c r="AO6" s="12">
+        <v>0</v>
+      </c>
+      <c r="AP6" s="12">
+        <v>0</v>
+      </c>
+      <c r="AQ6" s="12">
+        <v>0</v>
+      </c>
+      <c r="AR6" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS6" s="12">
+        <v>0</v>
+      </c>
+      <c r="AT6" s="12">
+        <v>0</v>
+      </c>
+      <c r="AU6" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV6" s="12">
+        <v>0</v>
+      </c>
+      <c r="AW6" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX6" s="12">
+        <v>0</v>
+      </c>
+      <c r="AY6" s="12">
+        <v>0</v>
+      </c>
+      <c r="AZ6" s="12">
+        <v>0</v>
+      </c>
+      <c r="BA6" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:53" x14ac:dyDescent="0.25">
+      <c r="A7" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="12">
+        <v>0</v>
+      </c>
+      <c r="C7" s="12">
+        <v>0</v>
+      </c>
+      <c r="D7" s="12">
+        <v>0</v>
+      </c>
+      <c r="E7" s="12">
+        <v>0</v>
+      </c>
+      <c r="F7" s="12">
+        <v>0</v>
+      </c>
+      <c r="G7" s="12">
+        <v>0</v>
+      </c>
+      <c r="H7" s="12">
+        <v>0</v>
+      </c>
+      <c r="I7" s="12">
+        <v>0</v>
+      </c>
+      <c r="J7" s="12">
+        <v>0</v>
+      </c>
+      <c r="K7" s="12">
+        <v>0</v>
+      </c>
+      <c r="L7" s="12">
+        <v>0</v>
+      </c>
+      <c r="M7" s="12">
+        <v>0</v>
+      </c>
+      <c r="N7" s="12">
+        <v>0</v>
+      </c>
+      <c r="O7" s="12">
+        <v>0</v>
+      </c>
+      <c r="P7" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="12">
+        <v>0</v>
+      </c>
+      <c r="R7" s="12">
+        <v>0</v>
+      </c>
+      <c r="S7" s="12">
+        <v>0</v>
+      </c>
+      <c r="T7" s="12">
+        <v>0</v>
+      </c>
+      <c r="U7" s="12">
+        <v>0</v>
+      </c>
+      <c r="V7" s="12">
+        <v>0</v>
+      </c>
+      <c r="W7" s="12">
+        <v>0</v>
+      </c>
+      <c r="X7" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="12">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="12">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="12">
+        <v>0</v>
+      </c>
+      <c r="AH7" s="12">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="12">
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="12">
+        <v>0</v>
+      </c>
+      <c r="AK7" s="12">
+        <v>0</v>
+      </c>
+      <c r="AL7" s="12">
+        <v>0</v>
+      </c>
+      <c r="AM7" s="12">
+        <v>0</v>
+      </c>
+      <c r="AN7" s="12">
+        <v>0</v>
+      </c>
+      <c r="AO7" s="12">
+        <v>0</v>
+      </c>
+      <c r="AP7" s="12">
+        <v>0</v>
+      </c>
+      <c r="AQ7" s="12">
+        <v>0</v>
+      </c>
+      <c r="AR7" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS7" s="12">
+        <v>0</v>
+      </c>
+      <c r="AT7" s="12">
+        <v>0</v>
+      </c>
+      <c r="AU7" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV7" s="12">
+        <v>0</v>
+      </c>
+      <c r="AW7" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX7" s="12">
+        <v>0</v>
+      </c>
+      <c r="AY7" s="12">
+        <v>0</v>
+      </c>
+      <c r="AZ7" s="12">
+        <v>0</v>
+      </c>
+      <c r="BA7" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:53" x14ac:dyDescent="0.25">
+      <c r="A8" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="12">
+        <v>0</v>
+      </c>
+      <c r="C8" s="12">
+        <v>0</v>
+      </c>
+      <c r="D8" s="12">
+        <v>0</v>
+      </c>
+      <c r="E8" s="12">
+        <v>0</v>
+      </c>
+      <c r="F8" s="12">
+        <v>0</v>
+      </c>
+      <c r="G8" s="12">
+        <v>0</v>
+      </c>
+      <c r="H8" s="12">
+        <v>0</v>
+      </c>
+      <c r="I8" s="12">
+        <v>0</v>
+      </c>
+      <c r="J8" s="12">
+        <v>0</v>
+      </c>
+      <c r="K8" s="12">
+        <v>0</v>
+      </c>
+      <c r="L8" s="12">
+        <v>0</v>
+      </c>
+      <c r="M8" s="12">
+        <v>0</v>
+      </c>
+      <c r="N8" s="12">
+        <v>0</v>
+      </c>
+      <c r="O8" s="12">
+        <v>0</v>
+      </c>
+      <c r="P8" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="12">
+        <v>0</v>
+      </c>
+      <c r="R8" s="12">
+        <v>0</v>
+      </c>
+      <c r="S8" s="12">
+        <v>0</v>
+      </c>
+      <c r="T8" s="12">
+        <v>0</v>
+      </c>
+      <c r="U8" s="12">
+        <v>0</v>
+      </c>
+      <c r="V8" s="12">
+        <v>0</v>
+      </c>
+      <c r="W8" s="12">
+        <v>0</v>
+      </c>
+      <c r="X8" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="12">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="12">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="12">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="12">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="12">
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="12">
+        <v>0</v>
+      </c>
+      <c r="AK8" s="12">
+        <v>0</v>
+      </c>
+      <c r="AL8" s="12">
+        <v>0</v>
+      </c>
+      <c r="AM8" s="12">
+        <v>0</v>
+      </c>
+      <c r="AN8" s="12">
+        <v>0</v>
+      </c>
+      <c r="AO8" s="12">
+        <v>0</v>
+      </c>
+      <c r="AP8" s="12">
+        <v>0</v>
+      </c>
+      <c r="AQ8" s="12">
+        <v>0</v>
+      </c>
+      <c r="AR8" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS8" s="12">
+        <v>0</v>
+      </c>
+      <c r="AT8" s="12">
+        <v>0</v>
+      </c>
+      <c r="AU8" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV8" s="12">
+        <v>0</v>
+      </c>
+      <c r="AW8" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX8" s="12">
+        <v>0</v>
+      </c>
+      <c r="AY8" s="12">
+        <v>0</v>
+      </c>
+      <c r="AZ8" s="12">
+        <v>0</v>
+      </c>
+      <c r="BA8" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:53" x14ac:dyDescent="0.25">
+      <c r="A9" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="12">
+        <v>0</v>
+      </c>
+      <c r="C9" s="12">
+        <v>0</v>
+      </c>
+      <c r="D9" s="12">
+        <v>0</v>
+      </c>
+      <c r="E9" s="12">
+        <v>0</v>
+      </c>
+      <c r="F9" s="12">
+        <v>0</v>
+      </c>
+      <c r="G9" s="12">
+        <v>0</v>
+      </c>
+      <c r="H9" s="12">
+        <v>0</v>
+      </c>
+      <c r="I9" s="12">
+        <v>0</v>
+      </c>
+      <c r="J9" s="12">
+        <v>0</v>
+      </c>
+      <c r="K9" s="12">
+        <v>0</v>
+      </c>
+      <c r="L9" s="12">
+        <v>0</v>
+      </c>
+      <c r="M9" s="12">
+        <v>0</v>
+      </c>
+      <c r="N9" s="12">
+        <v>0</v>
+      </c>
+      <c r="O9" s="12">
+        <v>0</v>
+      </c>
+      <c r="P9" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="12">
+        <v>0</v>
+      </c>
+      <c r="R9" s="12">
+        <v>0</v>
+      </c>
+      <c r="S9" s="12">
+        <v>0</v>
+      </c>
+      <c r="T9" s="12">
+        <v>0</v>
+      </c>
+      <c r="U9" s="12">
+        <v>0</v>
+      </c>
+      <c r="V9" s="12">
+        <v>0</v>
+      </c>
+      <c r="W9" s="12">
+        <v>0</v>
+      </c>
+      <c r="X9" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="12">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="12">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="12">
+        <v>0</v>
+      </c>
+      <c r="AH9" s="12">
+        <v>0</v>
+      </c>
+      <c r="AI9" s="12">
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="12">
+        <v>0</v>
+      </c>
+      <c r="AK9" s="12">
+        <v>0</v>
+      </c>
+      <c r="AL9" s="12">
+        <v>0</v>
+      </c>
+      <c r="AM9" s="12">
+        <v>0</v>
+      </c>
+      <c r="AN9" s="12">
+        <v>0</v>
+      </c>
+      <c r="AO9" s="12">
+        <v>0</v>
+      </c>
+      <c r="AP9" s="12">
+        <v>0</v>
+      </c>
+      <c r="AQ9" s="12">
+        <v>0</v>
+      </c>
+      <c r="AR9" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS9" s="12">
+        <v>0</v>
+      </c>
+      <c r="AT9" s="12">
+        <v>0</v>
+      </c>
+      <c r="AU9" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV9" s="12">
+        <v>0</v>
+      </c>
+      <c r="AW9" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX9" s="12">
+        <v>0</v>
+      </c>
+      <c r="AY9" s="12">
+        <v>0</v>
+      </c>
+      <c r="AZ9" s="12">
+        <v>0</v>
+      </c>
+      <c r="BA9" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:53" x14ac:dyDescent="0.25">
+      <c r="A10" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="12">
+        <v>0</v>
+      </c>
+      <c r="C10" s="12">
+        <v>0</v>
+      </c>
+      <c r="D10" s="12">
+        <v>0</v>
+      </c>
+      <c r="E10" s="12">
+        <v>0</v>
+      </c>
+      <c r="F10" s="12">
+        <v>0</v>
+      </c>
+      <c r="G10" s="12">
+        <v>0</v>
+      </c>
+      <c r="H10" s="12">
+        <v>0</v>
+      </c>
+      <c r="I10" s="12">
+        <v>0</v>
+      </c>
+      <c r="J10" s="12">
+        <v>0</v>
+      </c>
+      <c r="K10" s="12">
+        <v>0</v>
+      </c>
+      <c r="L10" s="12">
+        <v>0</v>
+      </c>
+      <c r="M10" s="12">
+        <v>0</v>
+      </c>
+      <c r="N10" s="12">
+        <v>0</v>
+      </c>
+      <c r="O10" s="12">
+        <v>0</v>
+      </c>
+      <c r="P10" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="12">
+        <v>0</v>
+      </c>
+      <c r="R10" s="12">
+        <v>0</v>
+      </c>
+      <c r="S10" s="12">
+        <v>0</v>
+      </c>
+      <c r="T10" s="12">
+        <v>0</v>
+      </c>
+      <c r="U10" s="12">
+        <v>0</v>
+      </c>
+      <c r="V10" s="12">
+        <v>0</v>
+      </c>
+      <c r="W10" s="12">
+        <v>0</v>
+      </c>
+      <c r="X10" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="12">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="12">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF10" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG10" s="12">
+        <v>0</v>
+      </c>
+      <c r="AH10" s="12">
+        <v>0</v>
+      </c>
+      <c r="AI10" s="12">
+        <v>0</v>
+      </c>
+      <c r="AJ10" s="12">
+        <v>0</v>
+      </c>
+      <c r="AK10" s="12">
+        <v>0</v>
+      </c>
+      <c r="AL10" s="12">
+        <v>0</v>
+      </c>
+      <c r="AM10" s="12">
+        <v>0</v>
+      </c>
+      <c r="AN10" s="12">
+        <v>0</v>
+      </c>
+      <c r="AO10" s="12">
+        <v>0</v>
+      </c>
+      <c r="AP10" s="12">
+        <v>0</v>
+      </c>
+      <c r="AQ10" s="12">
+        <v>0</v>
+      </c>
+      <c r="AR10" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS10" s="12">
+        <v>0</v>
+      </c>
+      <c r="AT10" s="12">
+        <v>0</v>
+      </c>
+      <c r="AU10" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV10" s="12">
+        <v>0</v>
+      </c>
+      <c r="AW10" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX10" s="12">
+        <v>0</v>
+      </c>
+      <c r="AY10" s="12">
+        <v>0</v>
+      </c>
+      <c r="AZ10" s="12">
+        <v>0</v>
+      </c>
+      <c r="BA10" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:53" x14ac:dyDescent="0.25">
+      <c r="A11" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="12">
+        <v>0</v>
+      </c>
+      <c r="C11" s="12">
+        <v>0</v>
+      </c>
+      <c r="D11" s="12">
+        <v>0</v>
+      </c>
+      <c r="E11" s="12">
+        <v>0</v>
+      </c>
+      <c r="F11" s="12">
+        <v>0</v>
+      </c>
+      <c r="G11" s="12">
+        <v>0</v>
+      </c>
+      <c r="H11" s="12">
+        <v>0</v>
+      </c>
+      <c r="I11" s="12">
+        <v>0</v>
+      </c>
+      <c r="J11" s="12">
+        <v>0</v>
+      </c>
+      <c r="K11" s="12">
+        <v>0</v>
+      </c>
+      <c r="L11" s="12">
+        <v>0</v>
+      </c>
+      <c r="M11" s="12">
+        <v>0</v>
+      </c>
+      <c r="N11" s="12">
+        <v>0</v>
+      </c>
+      <c r="O11" s="12">
+        <v>0</v>
+      </c>
+      <c r="P11" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="12">
+        <v>0</v>
+      </c>
+      <c r="R11" s="12">
+        <v>0</v>
+      </c>
+      <c r="S11" s="12">
+        <v>0</v>
+      </c>
+      <c r="T11" s="12">
+        <v>0</v>
+      </c>
+      <c r="U11" s="12">
+        <v>0</v>
+      </c>
+      <c r="V11" s="12">
+        <v>0</v>
+      </c>
+      <c r="W11" s="12">
+        <v>0</v>
+      </c>
+      <c r="X11" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AH11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AI11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AJ11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AK11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AL11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AM11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AN11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AO11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AP11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AQ11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AR11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AT11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AU11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AW11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AY11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AZ11" s="12">
+        <v>0</v>
+      </c>
+      <c r="BA11" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:53" x14ac:dyDescent="0.25">
+      <c r="A12" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="12">
+        <v>0</v>
+      </c>
+      <c r="C12" s="12">
+        <v>0</v>
+      </c>
+      <c r="D12" s="12">
+        <v>0</v>
+      </c>
+      <c r="E12" s="12">
+        <v>0</v>
+      </c>
+      <c r="F12" s="12">
+        <v>0</v>
+      </c>
+      <c r="G12" s="12">
+        <v>0</v>
+      </c>
+      <c r="H12" s="12">
+        <v>0</v>
+      </c>
+      <c r="I12" s="12">
+        <v>0</v>
+      </c>
+      <c r="J12" s="12">
+        <v>0</v>
+      </c>
+      <c r="K12" s="12">
+        <v>0</v>
+      </c>
+      <c r="L12" s="12">
+        <v>0</v>
+      </c>
+      <c r="M12" s="12">
+        <v>0</v>
+      </c>
+      <c r="N12" s="12">
+        <v>0</v>
+      </c>
+      <c r="O12" s="12">
+        <v>0</v>
+      </c>
+      <c r="P12" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="12">
+        <v>0</v>
+      </c>
+      <c r="R12" s="12">
+        <v>0</v>
+      </c>
+      <c r="S12" s="12">
+        <v>0</v>
+      </c>
+      <c r="T12" s="12">
+        <v>0</v>
+      </c>
+      <c r="U12" s="12">
+        <v>0</v>
+      </c>
+      <c r="V12" s="12">
+        <v>0</v>
+      </c>
+      <c r="W12" s="12">
+        <v>0</v>
+      </c>
+      <c r="X12" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="12">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="12">
+        <v>0</v>
+      </c>
+      <c r="AE12" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF12" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG12" s="12">
+        <v>0</v>
+      </c>
+      <c r="AH12" s="12">
+        <v>0</v>
+      </c>
+      <c r="AI12" s="12">
+        <v>0</v>
+      </c>
+      <c r="AJ12" s="12">
+        <v>0</v>
+      </c>
+      <c r="AK12" s="12">
+        <v>0</v>
+      </c>
+      <c r="AL12" s="12">
+        <v>0</v>
+      </c>
+      <c r="AM12" s="12">
+        <v>0</v>
+      </c>
+      <c r="AN12" s="12">
+        <v>0</v>
+      </c>
+      <c r="AO12" s="12">
+        <v>0</v>
+      </c>
+      <c r="AP12" s="12">
+        <v>0</v>
+      </c>
+      <c r="AQ12" s="12">
+        <v>0</v>
+      </c>
+      <c r="AR12" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS12" s="12">
+        <v>0</v>
+      </c>
+      <c r="AT12" s="12">
+        <v>0</v>
+      </c>
+      <c r="AU12" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV12" s="12">
+        <v>0</v>
+      </c>
+      <c r="AW12" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX12" s="12">
+        <v>0</v>
+      </c>
+      <c r="AY12" s="12">
+        <v>0</v>
+      </c>
+      <c r="AZ12" s="12">
+        <v>0</v>
+      </c>
+      <c r="BA12" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:53" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="12">
+        <v>0</v>
+      </c>
+      <c r="C13" s="12">
+        <v>0</v>
+      </c>
+      <c r="D13" s="12">
+        <v>0</v>
+      </c>
+      <c r="E13" s="12">
+        <v>0</v>
+      </c>
+      <c r="F13" s="12">
+        <v>0</v>
+      </c>
+      <c r="G13" s="12">
+        <v>0</v>
+      </c>
+      <c r="H13" s="12">
+        <v>0</v>
+      </c>
+      <c r="I13" s="12">
+        <v>0</v>
+      </c>
+      <c r="J13" s="12">
+        <v>0</v>
+      </c>
+      <c r="K13" s="12">
+        <v>0</v>
+      </c>
+      <c r="L13" s="12">
+        <v>0</v>
+      </c>
+      <c r="M13" s="12">
+        <v>0</v>
+      </c>
+      <c r="N13" s="12">
+        <v>0</v>
+      </c>
+      <c r="O13" s="12">
+        <v>0</v>
+      </c>
+      <c r="P13" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="12">
+        <v>0</v>
+      </c>
+      <c r="R13" s="12">
+        <v>0</v>
+      </c>
+      <c r="S13" s="12">
+        <v>0</v>
+      </c>
+      <c r="T13" s="12">
+        <v>0</v>
+      </c>
+      <c r="U13" s="12">
+        <v>0</v>
+      </c>
+      <c r="V13" s="12">
+        <v>0</v>
+      </c>
+      <c r="W13" s="12">
+        <v>0</v>
+      </c>
+      <c r="X13" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="12">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="12">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF13" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="12">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="12">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="12">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="12">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="12">
+        <v>0</v>
+      </c>
+      <c r="AL13" s="12">
+        <v>0</v>
+      </c>
+      <c r="AM13" s="12">
+        <v>0</v>
+      </c>
+      <c r="AN13" s="12">
+        <v>0</v>
+      </c>
+      <c r="AO13" s="12">
+        <v>0</v>
+      </c>
+      <c r="AP13" s="12">
+        <v>0</v>
+      </c>
+      <c r="AQ13" s="12">
+        <v>0</v>
+      </c>
+      <c r="AR13" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS13" s="12">
+        <v>0</v>
+      </c>
+      <c r="AT13" s="12">
+        <v>0</v>
+      </c>
+      <c r="AU13" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV13" s="12">
+        <v>0</v>
+      </c>
+      <c r="AW13" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX13" s="12">
+        <v>0</v>
+      </c>
+      <c r="AY13" s="12">
+        <v>0</v>
+      </c>
+      <c r="AZ13" s="12">
+        <v>0</v>
+      </c>
+      <c r="BA13" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:53" x14ac:dyDescent="0.25">
+      <c r="A14" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="12">
+        <v>0</v>
+      </c>
+      <c r="C14" s="12">
+        <v>0</v>
+      </c>
+      <c r="D14" s="12">
+        <v>0</v>
+      </c>
+      <c r="E14" s="12">
+        <v>0</v>
+      </c>
+      <c r="F14" s="12">
+        <v>0</v>
+      </c>
+      <c r="G14" s="12">
+        <v>0</v>
+      </c>
+      <c r="H14" s="12">
+        <v>0</v>
+      </c>
+      <c r="I14" s="12">
+        <v>0</v>
+      </c>
+      <c r="J14" s="12">
+        <v>0</v>
+      </c>
+      <c r="K14" s="12">
+        <v>0</v>
+      </c>
+      <c r="L14" s="12">
+        <v>0</v>
+      </c>
+      <c r="M14" s="12">
+        <v>0</v>
+      </c>
+      <c r="N14" s="12">
+        <v>0</v>
+      </c>
+      <c r="O14" s="12">
+        <v>0</v>
+      </c>
+      <c r="P14" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="12">
+        <v>0</v>
+      </c>
+      <c r="R14" s="12">
+        <v>0</v>
+      </c>
+      <c r="S14" s="12">
+        <v>0</v>
+      </c>
+      <c r="T14" s="12">
+        <v>0</v>
+      </c>
+      <c r="U14" s="12">
+        <v>0</v>
+      </c>
+      <c r="V14" s="12">
+        <v>0</v>
+      </c>
+      <c r="W14" s="12">
+        <v>0</v>
+      </c>
+      <c r="X14" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="12">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="12">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="12">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="12">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="12">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="12">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="12">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="12">
+        <v>0</v>
+      </c>
+      <c r="AM14" s="12">
+        <v>0</v>
+      </c>
+      <c r="AN14" s="12">
+        <v>0</v>
+      </c>
+      <c r="AO14" s="12">
+        <v>0</v>
+      </c>
+      <c r="AP14" s="12">
+        <v>0</v>
+      </c>
+      <c r="AQ14" s="12">
+        <v>0</v>
+      </c>
+      <c r="AR14" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS14" s="12">
+        <v>0</v>
+      </c>
+      <c r="AT14" s="12">
+        <v>0</v>
+      </c>
+      <c r="AU14" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV14" s="12">
+        <v>0</v>
+      </c>
+      <c r="AW14" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX14" s="12">
+        <v>0</v>
+      </c>
+      <c r="AY14" s="12">
+        <v>0</v>
+      </c>
+      <c r="AZ14" s="12">
+        <v>0</v>
+      </c>
+      <c r="BA14" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:53" x14ac:dyDescent="0.25">
+      <c r="A15" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="12">
+        <v>0</v>
+      </c>
+      <c r="C15" s="12">
+        <v>0</v>
+      </c>
+      <c r="D15" s="12">
+        <v>0</v>
+      </c>
+      <c r="E15" s="12">
+        <v>0</v>
+      </c>
+      <c r="F15" s="12">
+        <v>0</v>
+      </c>
+      <c r="G15" s="12">
+        <v>0</v>
+      </c>
+      <c r="H15" s="12">
+        <v>0</v>
+      </c>
+      <c r="I15" s="12">
+        <v>0</v>
+      </c>
+      <c r="J15" s="12">
+        <v>0</v>
+      </c>
+      <c r="K15" s="12">
+        <v>0</v>
+      </c>
+      <c r="L15" s="12">
+        <v>0</v>
+      </c>
+      <c r="M15" s="12">
+        <v>0</v>
+      </c>
+      <c r="N15" s="12">
+        <v>0</v>
+      </c>
+      <c r="O15" s="12">
+        <v>0</v>
+      </c>
+      <c r="P15" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="12">
+        <v>0</v>
+      </c>
+      <c r="R15" s="12">
+        <v>0</v>
+      </c>
+      <c r="S15" s="12">
+        <v>0</v>
+      </c>
+      <c r="T15" s="12">
+        <v>0</v>
+      </c>
+      <c r="U15" s="12">
+        <v>0</v>
+      </c>
+      <c r="V15" s="12">
+        <v>0</v>
+      </c>
+      <c r="W15" s="12">
+        <v>0</v>
+      </c>
+      <c r="X15" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="12">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="12">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF15" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="12">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="12">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="12">
+        <v>0</v>
+      </c>
+      <c r="AJ15" s="12">
+        <v>0</v>
+      </c>
+      <c r="AK15" s="12">
+        <v>0</v>
+      </c>
+      <c r="AL15" s="12">
+        <v>0</v>
+      </c>
+      <c r="AM15" s="12">
+        <v>0</v>
+      </c>
+      <c r="AN15" s="12">
+        <v>0</v>
+      </c>
+      <c r="AO15" s="12">
+        <v>0</v>
+      </c>
+      <c r="AP15" s="12">
+        <v>0</v>
+      </c>
+      <c r="AQ15" s="12">
+        <v>0</v>
+      </c>
+      <c r="AR15" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS15" s="12">
+        <v>0</v>
+      </c>
+      <c r="AT15" s="12">
+        <v>0</v>
+      </c>
+      <c r="AU15" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV15" s="12">
+        <v>0</v>
+      </c>
+      <c r="AW15" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX15" s="12">
+        <v>0</v>
+      </c>
+      <c r="AY15" s="12">
+        <v>0</v>
+      </c>
+      <c r="AZ15" s="12">
+        <v>0</v>
+      </c>
+      <c r="BA15" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:53" x14ac:dyDescent="0.25">
+      <c r="A16" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" s="12">
+        <v>0</v>
+      </c>
+      <c r="C16" s="12">
+        <v>0</v>
+      </c>
+      <c r="D16" s="12">
+        <v>0</v>
+      </c>
+      <c r="E16" s="12">
+        <v>0</v>
+      </c>
+      <c r="F16" s="12">
+        <v>0</v>
+      </c>
+      <c r="G16" s="12">
+        <v>0</v>
+      </c>
+      <c r="H16" s="12">
+        <v>0</v>
+      </c>
+      <c r="I16" s="12">
+        <v>0</v>
+      </c>
+      <c r="J16" s="12">
+        <v>0</v>
+      </c>
+      <c r="K16" s="12">
+        <v>0</v>
+      </c>
+      <c r="L16" s="12">
+        <v>0</v>
+      </c>
+      <c r="M16" s="12">
+        <v>0</v>
+      </c>
+      <c r="N16" s="12">
+        <v>0</v>
+      </c>
+      <c r="O16" s="12">
+        <v>0</v>
+      </c>
+      <c r="P16" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="12">
+        <v>0</v>
+      </c>
+      <c r="R16" s="12">
+        <v>0</v>
+      </c>
+      <c r="S16" s="12">
+        <v>0</v>
+      </c>
+      <c r="T16" s="12">
+        <v>0</v>
+      </c>
+      <c r="U16" s="12">
+        <v>0</v>
+      </c>
+      <c r="V16" s="12">
+        <v>0</v>
+      </c>
+      <c r="W16" s="12">
+        <v>0</v>
+      </c>
+      <c r="X16" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="12">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD16" s="12">
+        <v>0</v>
+      </c>
+      <c r="AE16" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF16" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG16" s="12">
+        <v>0</v>
+      </c>
+      <c r="AH16" s="12">
+        <v>0</v>
+      </c>
+      <c r="AI16" s="12">
+        <v>0</v>
+      </c>
+      <c r="AJ16" s="12">
+        <v>0</v>
+      </c>
+      <c r="AK16" s="12">
+        <v>0</v>
+      </c>
+      <c r="AL16" s="12">
+        <v>0</v>
+      </c>
+      <c r="AM16" s="12">
+        <v>0</v>
+      </c>
+      <c r="AN16" s="12">
+        <v>0</v>
+      </c>
+      <c r="AO16" s="12">
+        <v>0</v>
+      </c>
+      <c r="AP16" s="12">
+        <v>0</v>
+      </c>
+      <c r="AQ16" s="12">
+        <v>0</v>
+      </c>
+      <c r="AR16" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS16" s="12">
+        <v>0</v>
+      </c>
+      <c r="AT16" s="12">
+        <v>0</v>
+      </c>
+      <c r="AU16" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV16" s="12">
+        <v>0</v>
+      </c>
+      <c r="AW16" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX16" s="12">
+        <v>0</v>
+      </c>
+      <c r="AY16" s="12">
+        <v>0</v>
+      </c>
+      <c r="AZ16" s="12">
+        <v>0</v>
+      </c>
+      <c r="BA16" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:53" x14ac:dyDescent="0.25">
+      <c r="A17" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="12">
+        <v>0</v>
+      </c>
+      <c r="C17" s="12">
+        <v>0</v>
+      </c>
+      <c r="D17" s="12">
+        <v>0</v>
+      </c>
+      <c r="E17" s="12">
+        <v>0</v>
+      </c>
+      <c r="F17" s="12">
+        <v>0</v>
+      </c>
+      <c r="G17" s="12">
+        <v>0</v>
+      </c>
+      <c r="H17" s="12">
+        <v>0</v>
+      </c>
+      <c r="I17" s="12">
+        <v>0</v>
+      </c>
+      <c r="J17" s="12">
+        <v>0</v>
+      </c>
+      <c r="K17" s="12">
+        <v>0</v>
+      </c>
+      <c r="L17" s="12">
+        <v>0</v>
+      </c>
+      <c r="M17" s="12">
+        <v>0</v>
+      </c>
+      <c r="N17" s="12">
+        <v>0</v>
+      </c>
+      <c r="O17" s="12">
+        <v>0</v>
+      </c>
+      <c r="P17" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="12">
+        <v>0</v>
+      </c>
+      <c r="R17" s="12">
+        <v>0</v>
+      </c>
+      <c r="S17" s="12">
+        <v>0</v>
+      </c>
+      <c r="T17" s="12">
+        <v>0</v>
+      </c>
+      <c r="U17" s="12">
+        <v>0</v>
+      </c>
+      <c r="V17" s="12">
+        <v>0</v>
+      </c>
+      <c r="W17" s="12">
+        <v>0</v>
+      </c>
+      <c r="X17" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AE17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AH17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AI17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AJ17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AK17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AL17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AM17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AN17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AO17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AP17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AQ17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AR17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AT17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AU17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AW17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AY17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AZ17" s="12">
+        <v>0</v>
+      </c>
+      <c r="BA17" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:53" x14ac:dyDescent="0.25">
+      <c r="A18" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="12">
+        <v>0</v>
+      </c>
+      <c r="C18" s="12">
+        <v>0</v>
+      </c>
+      <c r="D18" s="12">
+        <v>0</v>
+      </c>
+      <c r="E18" s="12">
+        <v>0</v>
+      </c>
+      <c r="F18" s="12">
+        <v>0</v>
+      </c>
+      <c r="G18" s="12">
+        <v>0</v>
+      </c>
+      <c r="H18" s="12">
+        <v>0</v>
+      </c>
+      <c r="I18" s="12">
+        <v>0</v>
+      </c>
+      <c r="J18" s="12">
+        <v>0</v>
+      </c>
+      <c r="K18" s="12">
+        <v>0</v>
+      </c>
+      <c r="L18" s="12">
+        <v>0</v>
+      </c>
+      <c r="M18" s="12">
+        <v>0</v>
+      </c>
+      <c r="N18" s="12">
+        <v>0</v>
+      </c>
+      <c r="O18" s="12">
+        <v>0</v>
+      </c>
+      <c r="P18" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="12">
+        <v>0</v>
+      </c>
+      <c r="R18" s="12">
+        <v>0</v>
+      </c>
+      <c r="S18" s="12">
+        <v>0</v>
+      </c>
+      <c r="T18" s="12">
+        <v>0</v>
+      </c>
+      <c r="U18" s="12">
+        <v>0</v>
+      </c>
+      <c r="V18" s="12">
+        <v>0</v>
+      </c>
+      <c r="W18" s="12">
+        <v>0</v>
+      </c>
+      <c r="X18" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB18" s="12">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD18" s="12">
+        <v>0</v>
+      </c>
+      <c r="AE18" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF18" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG18" s="12">
+        <v>0</v>
+      </c>
+      <c r="AH18" s="12">
+        <v>0</v>
+      </c>
+      <c r="AI18" s="12">
+        <v>0</v>
+      </c>
+      <c r="AJ18" s="12">
+        <v>0</v>
+      </c>
+      <c r="AK18" s="12">
+        <v>0</v>
+      </c>
+      <c r="AL18" s="12">
+        <v>0</v>
+      </c>
+      <c r="AM18" s="12">
+        <v>0</v>
+      </c>
+      <c r="AN18" s="12">
+        <v>0</v>
+      </c>
+      <c r="AO18" s="12">
+        <v>0</v>
+      </c>
+      <c r="AP18" s="12">
+        <v>0</v>
+      </c>
+      <c r="AQ18" s="12">
+        <v>0</v>
+      </c>
+      <c r="AR18" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS18" s="12">
+        <v>0</v>
+      </c>
+      <c r="AT18" s="12">
+        <v>0</v>
+      </c>
+      <c r="AU18" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV18" s="12">
+        <v>0</v>
+      </c>
+      <c r="AW18" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX18" s="12">
+        <v>0</v>
+      </c>
+      <c r="AY18" s="12">
+        <v>0</v>
+      </c>
+      <c r="AZ18" s="12">
+        <v>0</v>
+      </c>
+      <c r="BA18" s="12">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor rgb="FF1E4E79"/>
   </sheetPr>
   <dimension ref="A1:BA1000"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.5" customWidth="1"/>
-    <col min="2" max="23" width="9.33203125" customWidth="1"/>
-    <col min="24" max="35" width="8.6640625" customWidth="1"/>
+    <col min="1" max="1" width="25.42578125" customWidth="1"/>
+    <col min="2" max="23" width="9.28515625" customWidth="1"/>
+    <col min="24" max="35" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>39</v>
       </c>
@@ -3571,7 +6491,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="2" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>22</v>
       </c>
@@ -3594,7 +6514,7 @@
         <v>0</v>
       </c>
       <c r="H2" s="10">
-        <v>4200</v>
+        <v>0</v>
       </c>
       <c r="I2" s="10">
         <v>0</v>
@@ -3609,7 +6529,7 @@
         <v>0</v>
       </c>
       <c r="M2" s="10">
-        <v>1900</v>
+        <v>0</v>
       </c>
       <c r="N2" s="10">
         <v>0</v>
@@ -3720,19 +6640,23 @@
         <v>0</v>
       </c>
       <c r="AX2" s="10">
+        <f>BCRbQ!AX2</f>
         <v>0</v>
       </c>
       <c r="AY2" s="10">
+        <f>BCRbQ!AY2</f>
         <v>0</v>
       </c>
       <c r="AZ2" s="10">
+        <f>BCRbQ!AZ2</f>
         <v>0</v>
       </c>
       <c r="BA2" s="10">
+        <f>BCRbQ!BA2</f>
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>23</v>
       </c>
@@ -3893,7 +6817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>24</v>
       </c>
@@ -4054,7 +6978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>25</v>
       </c>
@@ -4215,7 +7139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>26</v>
       </c>
@@ -4376,7 +7300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>27</v>
       </c>
@@ -4537,7 +7461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>28</v>
       </c>
@@ -4698,7 +7622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>29</v>
       </c>
@@ -4859,7 +7783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>30</v>
       </c>
@@ -5020,7 +7944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>31</v>
       </c>
@@ -5181,7 +8105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>32</v>
       </c>
@@ -5342,7 +8266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>34</v>
       </c>
@@ -5503,7 +8427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
         <v>35</v>
       </c>
@@ -5664,7 +8588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>36</v>
       </c>
@@ -5825,7 +8749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>37</v>
       </c>
@@ -5986,7 +8910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>38</v>
       </c>
@@ -6147,989 +9071,989 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="19" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="20" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="21" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="22" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="23" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="24" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="25" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="26" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="27" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="28" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="30" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="31" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="34" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="36" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="37" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="38" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="39" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="40" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="41" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="42" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="43" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="44" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="46" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="47" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="48" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="49" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="50" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="51" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="54" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="55" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="56" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="57" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="58" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="59" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="60" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="61" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="62" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="63" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="64" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="65" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="66" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="67" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="68" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="69" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="70" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="71" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="72" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="73" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="74" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="75" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="76" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="77" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="78" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="79" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="80" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="81" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="82" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="83" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="84" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="85" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="86" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="87" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="88" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="89" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="90" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="91" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="92" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="93" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="94" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="95" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="96" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="97" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="98" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="99" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="100" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="101" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="102" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="103" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="104" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="105" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="106" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="107" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="108" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="109" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="110" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="111" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="112" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="113" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="114" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="115" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="116" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="117" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="118" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="119" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="120" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="121" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="122" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="123" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="124" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="125" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="126" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="127" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="128" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="129" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="130" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="131" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="132" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="133" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="134" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="135" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="136" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="137" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="138" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="139" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="140" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="141" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="142" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="143" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="144" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="145" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="146" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="147" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="148" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="149" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="150" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="151" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="152" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="153" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="154" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="155" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="156" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="157" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="158" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="159" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="160" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="161" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="162" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="163" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="164" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="165" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="166" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="167" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="168" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="169" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="170" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="171" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="172" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="173" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="174" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="175" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="176" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="177" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="178" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="179" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="180" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="181" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="182" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="183" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="184" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="185" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="186" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="187" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="188" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="189" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="190" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="191" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="192" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="193" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="194" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="195" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="196" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="197" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="198" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="199" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="200" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="201" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="202" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="203" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="204" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="205" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="206" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="207" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="208" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="209" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="210" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="211" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="212" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="213" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="214" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="215" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="216" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="217" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="218" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="219" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="220" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="221" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="222" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="223" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="224" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="225" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="226" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="227" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="228" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="229" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="230" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="231" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="232" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="233" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="234" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="235" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="236" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="237" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="238" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="239" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="240" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="241" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="242" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="243" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="244" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="245" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="246" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="247" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="248" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="249" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="250" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="251" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="252" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="253" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="254" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="255" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="256" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="257" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="258" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="259" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="260" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="261" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="262" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="263" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="264" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="265" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="266" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="267" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="268" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="269" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="270" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="271" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="272" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="273" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="274" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="275" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="276" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="277" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="278" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="279" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="280" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="281" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="282" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="283" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="284" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="285" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="286" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="287" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="288" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="289" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="290" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="291" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="292" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="293" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="294" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="295" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="296" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="297" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="298" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="299" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="300" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="301" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="302" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="303" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="304" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="305" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="306" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="307" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="308" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="309" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="310" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="311" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="312" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="313" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="314" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="315" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="316" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="317" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="318" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="319" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="320" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="321" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="322" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="323" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="324" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="325" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="326" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="327" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="328" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="329" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="330" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="331" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="332" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="333" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="334" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="335" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="336" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="337" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="338" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="339" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="340" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="341" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="342" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="343" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="344" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="345" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="346" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="347" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="348" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="349" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="350" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="351" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="352" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="353" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="354" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="355" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="356" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="357" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="358" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="359" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="360" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="361" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="362" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="363" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="364" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="365" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="366" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="367" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="368" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="369" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="370" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="371" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="372" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="373" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="374" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="375" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="376" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="377" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="378" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="379" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="380" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="381" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="382" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="383" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="384" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="385" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="386" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="387" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="388" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="389" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="390" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="391" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="392" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="393" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="394" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="395" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="396" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="397" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="398" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="399" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="400" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="401" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="402" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="403" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="404" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="405" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="406" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="407" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="408" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="409" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="410" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="411" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="412" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="413" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="414" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="415" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="416" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="417" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="418" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="419" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="420" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="421" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="422" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="423" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="424" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="425" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="426" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="427" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="428" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="429" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="430" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="431" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="432" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="433" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="434" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="435" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="436" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="437" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="438" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="439" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="440" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="441" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="442" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="443" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="444" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="445" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="446" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="447" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="448" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="449" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="450" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="451" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="452" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="453" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="454" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="455" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="456" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="457" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="458" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="459" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="460" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="461" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="462" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="463" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="464" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="465" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="466" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="467" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="468" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="469" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="470" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="471" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="472" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="473" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="474" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="475" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="476" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="477" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="478" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="479" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="480" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="481" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="482" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="483" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="484" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="485" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="486" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="487" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="488" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="489" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="490" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="491" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="492" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="493" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="494" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="495" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="496" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="497" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="498" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="499" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="500" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="501" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="502" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="503" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="504" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="505" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="506" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="507" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="508" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="509" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="510" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="511" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="512" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="513" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="514" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="515" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="516" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="517" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="518" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="519" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="520" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="521" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="522" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="523" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="524" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="525" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="526" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="527" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="528" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="529" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="530" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="531" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="532" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="533" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="534" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="535" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="536" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="537" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="538" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="539" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="540" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="541" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="542" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="543" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="544" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="545" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="546" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="547" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="548" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="549" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="550" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="551" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="552" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="553" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="554" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="555" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="556" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="557" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="558" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="559" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="560" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="561" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="562" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="563" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="564" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="565" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="566" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="567" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="568" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="569" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="570" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="571" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="572" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="573" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="574" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="575" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="576" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="577" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="578" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="579" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="580" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="581" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="582" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="583" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="584" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="585" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="586" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="587" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="588" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="589" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="590" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="591" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="592" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="593" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="594" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="595" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="596" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="597" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="598" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="599" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="600" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="601" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="602" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="603" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="604" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="605" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="606" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="607" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="608" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="609" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="610" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="611" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="612" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="613" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="614" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="615" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="616" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="617" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="618" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="619" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="620" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="621" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="622" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="623" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="624" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="625" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="626" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="627" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="628" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="629" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="630" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="631" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="632" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="633" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="634" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="635" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="636" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="637" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="638" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="639" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="640" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="641" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="642" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="643" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="644" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="645" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="646" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="647" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="648" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="649" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="650" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="651" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="652" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="653" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="654" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="655" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="656" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="657" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="658" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="659" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="660" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="661" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="662" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="663" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="664" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="665" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="666" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="667" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="668" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="669" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="670" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="671" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="672" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="673" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="674" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="675" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="676" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="677" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="678" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="679" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="680" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="681" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="682" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="683" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="684" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="685" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="686" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="687" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="688" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="689" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="690" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="691" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="692" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="693" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="694" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="695" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="696" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="697" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="698" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="699" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="700" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="701" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="702" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="703" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="704" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="705" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="706" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="707" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="708" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="709" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="710" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="711" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="712" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="713" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="714" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="715" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="716" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="717" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="718" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="719" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="720" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="721" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="722" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="723" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="724" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="725" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="726" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="727" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="728" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="729" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="730" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="731" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="732" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="733" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="734" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="735" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="736" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="737" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="738" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="739" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="740" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="741" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="742" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="743" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="744" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="745" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="746" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="747" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="748" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="749" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="750" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="751" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="752" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="753" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="754" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="755" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="756" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="757" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="758" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="759" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="760" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="761" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="762" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="763" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="764" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="765" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="766" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="767" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="768" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="769" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="770" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="771" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="772" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="773" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="774" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="775" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="776" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="777" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="778" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="779" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="780" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="781" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="782" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="783" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="784" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="785" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="786" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="787" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="788" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="789" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="790" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="791" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="792" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="793" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="794" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="795" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="796" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="797" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="798" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="799" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="800" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="801" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="802" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="803" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="804" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="805" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="806" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="807" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="808" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="809" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="810" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="811" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="812" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="813" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="814" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="815" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="816" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="817" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="818" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="819" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="820" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="821" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="822" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="823" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="824" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="825" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="826" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="827" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="828" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="829" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="830" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="831" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="832" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="833" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="834" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="835" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="836" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="837" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="838" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="839" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="840" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="841" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="842" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="843" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="844" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="845" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="846" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="847" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="848" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="849" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="850" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="851" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="852" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="853" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="854" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="855" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="856" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="857" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="858" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="859" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="860" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="861" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="862" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="863" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="864" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="865" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="866" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="867" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="868" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="869" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="870" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="871" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="872" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="873" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="874" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="875" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="876" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="877" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="878" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="879" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="880" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="881" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="882" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="883" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="884" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="885" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="886" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="887" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="888" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="889" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="890" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="891" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="892" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="893" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="894" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="895" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="896" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="897" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="898" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="899" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="900" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="901" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="902" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="903" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="904" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="905" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="906" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="907" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="908" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="909" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="910" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="911" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="912" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="913" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="914" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="915" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="916" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="917" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="918" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="919" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="920" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="921" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="922" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="923" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="924" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="925" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="926" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="927" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="928" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="929" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="930" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="931" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="932" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="933" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="934" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="935" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="936" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="937" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="938" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="939" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="940" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="941" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="942" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="943" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="944" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="945" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="946" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="947" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="948" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="949" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="950" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="951" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="952" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="953" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="954" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="955" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="956" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="957" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="958" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="959" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="960" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="961" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="962" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="963" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="964" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="965" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="966" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="967" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="968" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="969" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="970" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="971" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="972" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="973" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="974" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="975" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="976" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="977" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="978" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="979" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="980" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="981" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="982" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="983" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="984" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="985" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="986" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="987" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="988" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="989" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="990" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="991" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="992" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="993" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="994" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="995" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="996" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="997" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="998" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="999" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1000" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="18" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="19" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="190" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="191" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="193" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="194" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="195" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="196" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="197" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="198" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="199" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="200" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="201" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="202" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="203" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="206" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="207" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="208" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="209" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="210" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="211" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="213" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="223" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="225" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="227" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="229" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="231" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="232" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="233" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="234" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="235" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="237" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="238" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="239" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="240" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="241" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="242" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="243" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="244" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="245" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="246" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="247" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="248" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="249" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="250" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="251" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="252" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="253" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="254" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="255" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="256" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="257" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="258" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="259" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="260" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="261" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="262" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="263" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="264" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="265" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="266" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="267" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="268" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="269" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="270" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="271" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="272" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="273" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="274" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="275" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="276" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="277" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="278" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="279" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="280" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="281" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="282" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="283" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="284" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="285" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="286" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="287" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="288" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="289" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="290" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="291" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="292" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="293" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="294" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="295" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="296" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="297" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="298" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="299" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="300" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="301" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="302" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="303" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="304" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="305" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="306" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="307" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="308" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="309" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="310" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="311" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="312" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="313" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="314" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="315" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="316" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="317" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="318" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="319" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="320" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="321" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="322" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="323" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="324" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="325" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="326" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="327" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="328" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="329" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="330" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="331" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="332" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="333" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="334" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="335" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="336" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="337" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="338" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="339" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="340" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="341" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="342" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="343" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="344" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="345" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="346" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="347" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="348" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="349" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="350" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="351" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="352" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="353" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="354" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="355" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="356" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="357" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="358" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="359" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="360" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="361" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="362" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="363" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="364" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="365" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="366" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="367" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="368" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="369" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="370" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="371" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="372" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="373" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="374" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="375" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="376" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="377" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="378" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="379" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="380" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="381" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="382" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="383" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="384" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="385" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="386" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="387" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="388" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="389" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="390" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="391" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="392" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="393" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="394" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="395" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="396" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="397" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="398" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="399" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="400" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="401" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="402" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="403" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="404" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="405" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="406" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="407" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="408" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="409" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="410" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="411" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="412" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="413" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="414" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="415" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="416" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="417" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="418" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="419" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="420" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="421" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="422" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="423" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="424" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="425" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="426" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="427" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="428" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="429" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="430" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="431" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="432" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="433" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="434" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="435" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="436" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="437" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="438" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="439" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="440" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="441" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="442" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="443" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="444" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="445" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="446" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="447" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="448" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="449" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="450" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="451" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="452" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="453" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="454" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="455" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="456" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="457" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="458" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="459" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="460" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="461" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="462" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="463" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="464" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="465" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="466" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="467" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="468" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="469" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="470" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="471" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="472" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="473" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="474" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="475" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="476" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="477" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="478" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="479" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="480" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="481" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="482" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="483" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="484" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="485" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="486" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="487" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="488" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="489" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="490" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="491" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="492" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="493" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="494" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="495" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="496" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="497" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="498" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="499" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="500" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="501" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="502" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="503" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="504" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="505" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="506" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="507" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="508" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="509" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="510" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="511" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="512" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="513" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="514" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="515" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="516" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="517" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="518" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="519" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="520" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="521" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="522" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="523" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="524" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="525" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="526" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="527" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="528" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="529" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="530" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="531" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="532" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="533" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="534" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="535" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="536" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="537" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="538" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="539" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="540" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="541" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="542" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="543" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="544" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="545" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="546" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="547" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="548" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="549" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="550" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="551" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="552" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="553" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="554" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="555" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="556" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="557" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="558" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="559" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="560" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="561" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="562" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="563" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="564" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="565" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="566" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="567" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="568" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="569" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="570" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="571" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="572" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="573" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="574" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="575" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="576" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="577" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="578" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="579" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="580" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="581" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="582" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="583" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="584" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="585" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="586" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="587" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="588" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="589" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="590" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="591" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="592" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="593" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="594" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="595" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="596" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="597" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="598" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="599" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="600" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="601" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="602" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="603" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="604" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="605" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="606" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="607" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="608" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="609" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="610" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="611" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="612" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="613" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="614" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="615" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="616" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="617" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="618" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="619" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="620" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="621" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="622" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="623" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="624" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="625" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="626" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="627" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="628" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="629" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="630" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="631" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="632" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="633" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="634" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="635" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="636" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="637" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="638" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="639" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="640" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="641" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="642" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="643" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="644" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="645" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="646" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="647" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="648" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="649" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="650" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="651" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="652" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="653" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="654" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="655" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="656" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="657" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="658" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="659" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="660" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="661" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="662" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="663" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="664" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="665" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="666" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="667" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="668" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="669" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="670" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="671" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="672" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="673" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="674" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="675" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="676" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="677" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="678" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="679" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="680" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="681" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="682" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="683" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="684" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="685" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="686" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="687" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="688" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="689" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="690" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="691" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="692" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="693" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="694" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="695" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="696" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="697" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="698" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="699" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="700" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="701" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="702" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="703" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="704" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="705" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="706" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="707" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="708" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="709" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="710" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="711" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="712" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="713" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="714" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="715" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="716" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="717" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="718" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="719" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="720" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="721" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="722" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="723" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="724" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="725" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="726" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="727" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="728" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="729" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="730" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="731" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="732" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="733" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="734" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="735" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="736" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="737" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="738" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="739" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="740" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="741" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="742" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="743" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="744" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="745" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="746" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="747" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="748" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="749" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="750" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="751" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="752" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="753" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="754" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="755" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="756" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="757" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="758" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="759" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="760" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="761" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="762" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="763" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="764" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="765" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="766" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="767" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="768" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="769" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="770" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="771" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="772" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="773" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="774" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="775" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="776" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="777" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="778" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="779" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="780" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="781" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="782" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="783" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="784" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="785" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="786" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="787" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="788" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="789" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="790" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="791" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="792" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="793" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="794" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="795" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="796" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="797" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="798" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="799" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="800" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="801" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="802" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="803" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="804" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="805" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="806" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="807" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="808" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="809" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="810" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="811" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="812" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="813" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="814" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="815" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="816" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="817" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="818" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="819" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="820" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="821" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="822" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="823" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="824" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="825" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="826" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="827" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="828" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="829" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="830" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="831" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="832" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="833" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="834" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="835" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="836" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="837" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="838" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="839" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="840" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="841" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="842" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="843" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="844" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="845" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="846" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="847" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="848" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="849" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="850" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="851" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="852" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="853" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="854" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="855" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="856" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="857" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="858" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="859" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="860" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="861" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="862" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="863" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="864" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="865" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="866" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="867" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="868" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="869" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="870" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="871" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="872" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="873" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="874" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="875" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="876" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="877" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="878" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="879" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="880" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="881" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="882" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="883" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="884" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="885" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="886" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="887" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="888" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="889" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="890" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="891" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="892" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="893" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="894" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="895" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="896" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="897" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="898" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="899" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="900" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="901" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="902" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="903" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="904" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="905" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="906" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="907" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="908" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="909" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="910" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="911" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="912" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="913" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="914" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="915" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="916" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="917" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="918" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="919" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="920" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="921" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="922" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="923" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="924" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="925" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="926" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="927" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="928" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="929" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="930" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="931" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="932" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="933" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="934" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="935" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="936" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="937" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="938" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="939" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="940" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="941" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="942" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="943" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="944" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="945" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="946" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="947" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="948" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="949" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="950" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="951" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="952" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="953" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="954" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="955" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="956" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="957" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="958" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="959" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="960" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="961" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="962" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="963" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="964" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="965" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="966" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="967" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="968" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="969" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="970" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="971" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="972" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="973" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="974" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="975" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="976" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="977" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="978" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="979" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="980" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="981" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="982" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="983" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="984" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="985" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="986" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="987" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="988" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="989" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="990" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="991" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="992" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="993" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="994" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="995" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="996" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="997" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="998" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="999" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1000" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="portrait"/>
